--- a/output/yearly_surface_area_iteration_8_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_8_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497649647331</v>
+        <v>10.84497626464536</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907251426362</v>
+        <v>37.78907170646444</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.541384953396497</v>
+        <v>3.572579895754143</v>
       </c>
       <c r="C2" t="n">
-        <v>6.090762757147212</v>
+        <v>17.2689421177014</v>
       </c>
       <c r="D2" t="n">
-        <v>20.78458064660922</v>
+        <v>31.32069700858599</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.15880644837651</v>
+        <v>13.73955912093411</v>
       </c>
       <c r="C3" t="n">
-        <v>29.44261365036184</v>
+        <v>28.99100970640831</v>
       </c>
       <c r="D3" t="n">
-        <v>70.57293371978197</v>
+        <v>58.35508354043041</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.3347035183527</v>
+        <v>28.94584931201296</v>
       </c>
       <c r="C4" t="n">
-        <v>62.11615899539994</v>
+        <v>92.96365361053896</v>
       </c>
       <c r="D4" t="n">
-        <v>96.97114773927444</v>
+        <v>65.38341535513332</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.79286090106649</v>
+        <v>35.76016012719008</v>
       </c>
       <c r="C5" t="n">
-        <v>94.12506114466295</v>
+        <v>161.595672119025</v>
       </c>
       <c r="D5" t="n">
-        <v>70.98035901704441</v>
+        <v>47.95837535245669</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.74725853831463</v>
+        <v>32.40258297866598</v>
       </c>
       <c r="C6" t="n">
-        <v>102.8429807583746</v>
+        <v>192.8054316370311</v>
       </c>
       <c r="D6" t="n">
-        <v>48.62400029593603</v>
+        <v>39.40637110076273</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.52409870981433</v>
+        <v>22.51736534460484</v>
       </c>
       <c r="C7" t="n">
-        <v>91.32708018755953</v>
+        <v>173.7310554912198</v>
       </c>
       <c r="D7" t="n">
-        <v>39.58504918293564</v>
+        <v>37.96811071404115</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.0207398749762</v>
+        <v>12.10004045484194</v>
       </c>
       <c r="C8" t="n">
-        <v>58.58088551240717</v>
+        <v>113.9907259400971</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30012136452581</v>
+        <v>35.13184159647211</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.654686850012379</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
+        <v>55.24687030878498</v>
+      </c>
+      <c r="D9" t="n">
         <v>33.72499713628642</v>
-      </c>
-      <c r="D9" t="n">
-        <v>34.16874709860598</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>29.04009709162065</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.97566159603886</v>
       </c>
       <c r="D13" t="n">
         <v>32.5203927031756</v>
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>22.73924032576462</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.701699711755612</v>
+        <v>7.650892531366663</v>
       </c>
       <c r="C21" t="n">
-        <v>95.30853393297571</v>
+        <v>92.76707194282079</v>
       </c>
       <c r="D21" t="n">
-        <v>8.664412175725063</v>
+        <v>7.650892531366663</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.924487542231006</v>
+        <v>5.062872910800801</v>
       </c>
       <c r="C2" t="n">
-        <v>9.044841599225864</v>
+        <v>11.66119923104361</v>
       </c>
       <c r="D2" t="n">
-        <v>35.04642954620264</v>
+        <v>33.07802539918778</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.7148765596077</v>
+        <v>12.7136327699962</v>
       </c>
       <c r="C3" t="n">
-        <v>26.27156856564465</v>
+        <v>47.21224709722911</v>
       </c>
       <c r="D3" t="n">
-        <v>70.36185796336891</v>
+        <v>67.1024555852695</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.58621085708914</v>
+        <v>27.15906849028376</v>
       </c>
       <c r="C4" t="n">
-        <v>67.88490850555419</v>
+        <v>83.08530821040756</v>
       </c>
       <c r="D4" t="n">
-        <v>107.2068493037517</v>
+        <v>76.65289725218247</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.45616249623884</v>
+        <v>39.14718970684157</v>
       </c>
       <c r="C5" t="n">
-        <v>103.1571400237336</v>
+        <v>164.0991287648544</v>
       </c>
       <c r="D5" t="n">
-        <v>87.67006998924018</v>
+        <v>57.23589115758906</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.05797383894213</v>
+        <v>38.96360288614742</v>
       </c>
       <c r="C6" t="n">
-        <v>125.5449146713779</v>
+        <v>219.6130344491945</v>
       </c>
       <c r="D6" t="n">
-        <v>57.88188114698346</v>
+        <v>44.51833139677587</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.46527596301753</v>
+        <v>29.2845522699781</v>
       </c>
       <c r="C7" t="n">
-        <v>118.1562814492164</v>
+        <v>221.2810237987098</v>
       </c>
       <c r="D7" t="n">
-        <v>44.31609136970101</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.86490403190821</v>
+        <v>17.27385085622263</v>
       </c>
       <c r="C8" t="n">
-        <v>88.78926237208152</v>
+        <v>164.2267559664064</v>
       </c>
       <c r="D8" t="n">
-        <v>38.30288668118931</v>
+        <v>37.1346069131356</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.20468654856884</v>
+        <v>8.985936736971052</v>
       </c>
       <c r="C9" t="n">
-        <v>51.9187455913883</v>
+        <v>92.96561710594743</v>
       </c>
       <c r="D9" t="n">
-        <v>35.83280945730432</v>
+        <v>34.61249706092553</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>5.836490101747287</v>
       </c>
       <c r="C10" t="n">
-        <v>34.87658719336794</v>
+        <v>46.54956739686252</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>31.8076438698924</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.8092064546734</v>
+        <v>29.94134148411922</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>27.0569667290421</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.886600346181607</v>
+        <v>7.817459102982864</v>
       </c>
       <c r="C21" t="n">
-        <v>104.4974545869063</v>
+        <v>100.6497859509044</v>
       </c>
       <c r="D21" t="n">
-        <v>9.858250432727008</v>
+        <v>8.794641490855721</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.988301143007048</v>
+        <v>4.946044933995431</v>
       </c>
       <c r="C2" t="n">
-        <v>10.95237738857742</v>
+        <v>12.73130422867264</v>
       </c>
       <c r="D2" t="n">
-        <v>29.85200244303276</v>
+        <v>29.67725135167683</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.24702487303848</v>
+        <v>14.1273494641116</v>
       </c>
       <c r="C3" t="n">
-        <v>30.25746424488669</v>
+        <v>45.87707021945345</v>
       </c>
       <c r="D3" t="n">
-        <v>79.16813487046279</v>
+        <v>73.92069339126358</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.05843150283185</v>
+        <v>25.1170332654504</v>
       </c>
       <c r="C4" t="n">
-        <v>65.99602592258334</v>
+        <v>96.54997797415255</v>
       </c>
       <c r="D4" t="n">
-        <v>115.5791937255685</v>
+        <v>86.722683454642</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.38882281527331</v>
+        <v>39.34353924769093</v>
       </c>
       <c r="C5" t="n">
-        <v>111.8456072063179</v>
+        <v>158.9694970101648</v>
       </c>
       <c r="D5" t="n">
-        <v>101.2181883078462</v>
+        <v>67.59332943739291</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.62528514327655</v>
+        <v>44.03531152628644</v>
       </c>
       <c r="C6" t="n">
-        <v>142.812875041375</v>
+        <v>234.1841338756257</v>
       </c>
       <c r="D6" t="n">
-        <v>69.47435803872979</v>
+        <v>49.67054334866313</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>50.06520592577034</v>
+        <v>35.75230614555609</v>
       </c>
       <c r="C7" t="n">
-        <v>145.1651425407504</v>
+        <v>258.2909487534061</v>
       </c>
       <c r="D7" t="n">
-        <v>49.10702016642545</v>
+        <v>42.51949307092936</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>31.37665662772806</v>
+        <v>22.94835258676919</v>
       </c>
       <c r="C8" t="n">
-        <v>119.1645363414778</v>
+        <v>214.7965802121596</v>
       </c>
       <c r="D8" t="n">
-        <v>41.0566889916016</v>
+        <v>39.05392367493811</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.30781111524376</v>
+        <v>12.09218647320796</v>
       </c>
       <c r="C9" t="n">
-        <v>76.65780599070366</v>
+        <v>137.1187383567435</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>46.26486056263094</v>
+        <v>70.18023463808325</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>35.89465956267188</v>
+        <v>40.69246059332603</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>30.95941385342317</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>19.26188995732242</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.055128759404914</v>
+        <v>7.966450390462477</v>
       </c>
       <c r="C21" t="n">
-        <v>112.7718026316688</v>
+        <v>107.5470802712434</v>
       </c>
       <c r="D21" t="n">
-        <v>11.07580204418176</v>
+        <v>9.958062988078096</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.119454424748621</v>
+        <v>4.659374604355362</v>
       </c>
       <c r="C2" t="n">
-        <v>7.35918079103409</v>
+        <v>9.064476553310801</v>
       </c>
       <c r="D2" t="n">
-        <v>24.48871473473244</v>
+        <v>24.5927799913826</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.24135537099124</v>
+        <v>16.77315952705676</v>
       </c>
       <c r="C3" t="n">
-        <v>46.28940425523712</v>
+        <v>66.04216806468294</v>
       </c>
       <c r="D3" t="n">
-        <v>86.18763095582749</v>
+        <v>77.26845306274521</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.12528815771187</v>
+        <v>18.90158854986384</v>
       </c>
       <c r="C4" t="n">
-        <v>92.56800928572751</v>
+        <v>129.4012196536594</v>
       </c>
       <c r="D4" t="n">
-        <v>112.426801847232</v>
+        <v>80.40513697781377</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.70478134512475</v>
+        <v>24.78912953223197</v>
       </c>
       <c r="C5" t="n">
-        <v>85.338419191654</v>
+        <v>139.9235915477767</v>
       </c>
       <c r="D5" t="n">
-        <v>69.67954330891737</v>
+        <v>47.19752088166541</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.07427833482005</v>
+        <v>22.1786623866397</v>
       </c>
       <c r="C6" t="n">
-        <v>95.59768270103318</v>
+        <v>170.1034977240279</v>
       </c>
       <c r="D6" t="n">
-        <v>32.32207966691774</v>
+        <v>27.97490083251287</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.78065365579224</v>
+        <v>15.21119892960008</v>
       </c>
       <c r="C7" t="n">
-        <v>83.78136733271855</v>
+        <v>151.0340303167378</v>
       </c>
       <c r="D7" t="n">
-        <v>28.86534600026472</v>
+        <v>27.42806736124739</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.26555490623215</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>56.4946716408827</v>
+        <v>101.0561999366454</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>26.20284622634736</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>35.27812200440487</v>
+        <v>53.58280795008665</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>28.04362317181014</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>29.04009709162065</v>
+        <v>28.18597658892593</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.60910984945629</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>26.90381408717959</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>21.853703896534</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>24.27567548291088</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>13.37631247036279</v>
       </c>
     </row>
     <row r="19">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.309291584566751</v>
+        <v>2.831360379047801</v>
       </c>
       <c r="C2" t="n">
-        <v>3.740458753180348</v>
+        <v>4.23525959612074</v>
       </c>
       <c r="D2" t="n">
-        <v>17.18745705824891</v>
+        <v>17.92376783643402</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>31.14594591723006</v>
+        <v>16.79770321966292</v>
       </c>
       <c r="C3" t="n">
-        <v>37.96909246174539</v>
+        <v>51.99826715543232</v>
       </c>
       <c r="D3" t="n">
-        <v>86.15326978617884</v>
+        <v>78.79016200432777</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.13049999586936</v>
+        <v>24.28745645536184</v>
       </c>
       <c r="C4" t="n">
-        <v>106.3772724936631</v>
+        <v>150.3576061485118</v>
       </c>
       <c r="D4" t="n">
-        <v>128.3163884404666</v>
+        <v>96.84352053772237</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.7054032399305</v>
+        <v>27.4889357189107</v>
       </c>
       <c r="C5" t="n">
-        <v>126.7927160034756</v>
+        <v>185.5503161026472</v>
       </c>
       <c r="D5" t="n">
-        <v>87.17919613711678</v>
+        <v>59.02758071783948</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.47429161880501</v>
+        <v>25.84156307118455</v>
       </c>
       <c r="C6" t="n">
-        <v>117.132318593687</v>
+        <v>197.7161336536737</v>
       </c>
       <c r="D6" t="n">
-        <v>40.73467574460867</v>
+        <v>32.72459622565894</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.52303484665207</v>
+        <v>14.19312656029614</v>
       </c>
       <c r="C7" t="n">
-        <v>106.2987326773234</v>
+        <v>189.2416874706151</v>
       </c>
       <c r="D7" t="n">
-        <v>31.56024344842221</v>
+        <v>29.8235317596096</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.429686699290613</v>
+        <v>7.093127163183205</v>
       </c>
       <c r="C8" t="n">
-        <v>75.52094214918588</v>
+        <v>130.8473340220149</v>
       </c>
       <c r="D8" t="n">
-        <v>28.37250865273282</v>
+        <v>26.95388322009618</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>4.104687151455913</v>
       </c>
       <c r="C9" t="n">
-        <v>41.04687151455913</v>
+        <v>55.80155776168444</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>28.06718511671205</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.46715734296802</v>
       </c>
     </row>
     <row r="11">
@@ -2150,10 +2150,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
         <v>29.49759152179966</v>
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.47965802121596</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>27.77167905773377</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.422192570555134</v>
+        <v>2.510328879759094</v>
       </c>
       <c r="C2" t="n">
-        <v>9.334457171978672</v>
+        <v>6.33423618780042</v>
       </c>
       <c r="D2" t="n">
-        <v>18.12502611580461</v>
+        <v>17.67734916266807</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.51914891356409</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="C3" t="n">
-        <v>25.42235680147115</v>
+        <v>34.25808613969245</v>
       </c>
       <c r="D3" t="n">
-        <v>81.01872929296803</v>
+        <v>75.00552460445631</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.30238795957057</v>
+        <v>27.74615361742335</v>
       </c>
       <c r="C4" t="n">
-        <v>100.3405058602495</v>
+        <v>140.2367690654314</v>
       </c>
       <c r="D4" t="n">
-        <v>138.7945816878928</v>
+        <v>110.4868683836403</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.88474427463818</v>
+        <v>31.34229545807943</v>
       </c>
       <c r="C5" t="n">
-        <v>162.7001382863027</v>
+        <v>227.4218556887737</v>
       </c>
       <c r="D5" t="n">
-        <v>110.569335190797</v>
+        <v>75.54548584179207</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.27682146153116</v>
+        <v>30.43025184083414</v>
       </c>
       <c r="C6" t="n">
-        <v>156.9412062531909</v>
+        <v>242.8382398885614</v>
       </c>
       <c r="D6" t="n">
-        <v>55.8692983532775</v>
+        <v>40.89568236810514</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.76364514965055</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="C7" t="n">
-        <v>137.260110026155</v>
+        <v>231.2820876618721</v>
       </c>
       <c r="D7" t="n">
-        <v>35.81219275551515</v>
+        <v>31.91956310817654</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.76901155206151</v>
+        <v>9.846929473595507</v>
       </c>
       <c r="C8" t="n">
-        <v>106.0631132283042</v>
+        <v>182.8357837004047</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>28.37250865273282</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.323436963053704</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>64.01093206459626</v>
+        <v>98.51249163494191</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>28.51093507903161</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>39.14718970684157</v>
+        <v>45.69544689416779</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2461,10 +2461,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
         <v>30.03068052520567</v>
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>26.03594911662541</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>18.21141991377833</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>16.84188186635403</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>10.38885420633975</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.233876937788994</v>
+        <v>1.533489914033518</v>
       </c>
       <c r="C2" t="n">
-        <v>4.271584261177872</v>
+        <v>3.129811681138832</v>
       </c>
       <c r="D2" t="n">
-        <v>12.49764827506189</v>
+        <v>12.47212283475148</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.25407703341745</v>
+        <v>12.65963664626262</v>
       </c>
       <c r="C3" t="n">
-        <v>31.9166178650638</v>
+        <v>32.56948008838793</v>
       </c>
       <c r="D3" t="n">
-        <v>80.14988257470961</v>
+        <v>74.72572650874598</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>54.20327249917065</v>
+        <v>30.32422308877548</v>
       </c>
       <c r="C4" t="n">
-        <v>97.3412666237755</v>
+        <v>135.5528507684698</v>
       </c>
       <c r="D4" t="n">
-        <v>150.0130127043211</v>
+        <v>119.6760268953904</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.3573658310084</v>
+        <v>32.39767424014475</v>
       </c>
       <c r="C5" t="n">
-        <v>192.2507441841317</v>
+        <v>276.190172897234</v>
       </c>
       <c r="D5" t="n">
-        <v>116.4352777236717</v>
+        <v>78.0734861802276</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.46800022195202</v>
+        <v>24.15099352447154</v>
       </c>
       <c r="C6" t="n">
-        <v>190.390332284584</v>
+        <v>277.0118957256886</v>
       </c>
       <c r="D6" t="n">
-        <v>54.6214970211798</v>
+        <v>40.73467574460867</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.102764713776425</v>
+        <v>6.527640485537042</v>
       </c>
       <c r="C7" t="n">
-        <v>142.1708120427976</v>
+        <v>239.905759495976</v>
       </c>
       <c r="D7" t="n">
-        <v>35.39298648580176</v>
+        <v>32.09922293805371</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.339324852770902</v>
+        <v>3.421390749300134</v>
       </c>
       <c r="C8" t="n">
-        <v>80.44440688598364</v>
+        <v>122.7528242004999</v>
       </c>
       <c r="D8" t="n">
-        <v>31.87734795689393</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>29.84218496599028</v>
+        <v>34.83437204208531</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>30.95155987178918</v>
       </c>
     </row>
     <row r="10">
@@ -2758,10 +2758,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>25.90832191507333</v>
+        <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
         <v>23.48831382410494</v>
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.7904711328347</v>
+        <v>19.19120412261664</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>22.56743447752142</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>14.75370449942107</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.968224220565608</v>
+        <v>1.443169125242811</v>
       </c>
       <c r="C2" t="n">
-        <v>2.80092620021615</v>
+        <v>8.107272541670159</v>
       </c>
       <c r="D2" t="n">
-        <v>14.69676313257475</v>
+        <v>10.14930776650353</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.70091110756999</v>
+        <v>9.184249773228911</v>
       </c>
       <c r="C3" t="n">
-        <v>24.03318379996192</v>
+        <v>22.76672926148353</v>
       </c>
       <c r="D3" t="n">
-        <v>72.35971454151115</v>
+        <v>68.95795874629596</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.03811790067893</v>
+        <v>27.68234001664731</v>
       </c>
       <c r="C4" t="n">
-        <v>89.35180380661495</v>
+        <v>110.2571394208465</v>
       </c>
       <c r="D4" t="n">
-        <v>154.9777108446972</v>
+        <v>126.7720993016864</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.9791152274329</v>
+        <v>37.65002445786519</v>
       </c>
       <c r="C5" t="n">
-        <v>187.8083358224148</v>
+        <v>266.5445017030091</v>
       </c>
       <c r="D5" t="n">
-        <v>140.4390090925062</v>
+        <v>96.13764393836894</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.50324532831367</v>
+        <v>30.95352336719769</v>
       </c>
       <c r="C6" t="n">
-        <v>243.2407564473025</v>
+        <v>346.5667570761666</v>
       </c>
       <c r="D6" t="n">
-        <v>72.2114706381699</v>
+        <v>51.07935130425731</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.06201433628357</v>
+        <v>13.1750541909922</v>
       </c>
       <c r="C7" t="n">
-        <v>201.5783291221806</v>
+        <v>308.5957011190126</v>
       </c>
       <c r="D7" t="n">
-        <v>41.20198765183014</v>
+        <v>35.39298648580176</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.9248473951295</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>124.5886924074415</v>
+        <v>195.5199640392735</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>55.57968278052466</v>
+        <v>73.55155625446676</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.34243432679967</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.98900515327081</v>
+        <v>22.56743447752142</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.45591614986479</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.44249047717483</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>7.852999886270235</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.851977080836984</v>
+        <v>0.9198975988792613</v>
       </c>
       <c r="C2" t="n">
-        <v>1.878083358224148</v>
+        <v>5.496805396077892</v>
       </c>
       <c r="D2" t="n">
-        <v>10.5429885959065</v>
+        <v>8.875980994095412</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.11047982669016</v>
+        <v>7.53491363009427</v>
       </c>
       <c r="C3" t="n">
-        <v>18.4224956701914</v>
+        <v>26.94897448157494</v>
       </c>
       <c r="D3" t="n">
-        <v>68.55544218755476</v>
+        <v>63.27363953870693</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.24384295021426</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="C4" t="n">
-        <v>78.37586447313562</v>
+        <v>92.01921231905354</v>
       </c>
       <c r="D4" t="n">
-        <v>156.2029319795973</v>
+        <v>131.9027128040802</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>69.85134915716057</v>
+        <v>40.37437433715008</v>
       </c>
       <c r="C5" t="n">
-        <v>185.2803354839793</v>
+        <v>250.8610821276663</v>
       </c>
       <c r="D5" t="n">
-        <v>157.0060016016712</v>
+        <v>108.3113154710294</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.7611261793611</v>
+        <v>35.09944392223197</v>
       </c>
       <c r="C6" t="n">
-        <v>273.3892466970178</v>
+        <v>386.5769030150411</v>
       </c>
       <c r="D6" t="n">
-        <v>86.42030516173399</v>
+        <v>59.65295400544471</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.74450891718435</v>
+        <v>11.73777555197486</v>
       </c>
       <c r="C7" t="n">
-        <v>254.5779789359446</v>
+        <v>374.2314256341374</v>
       </c>
       <c r="D7" t="n">
-        <v>46.95110220789945</v>
+        <v>39.28561613314036</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>3.504839304161113</v>
       </c>
       <c r="C8" t="n">
-        <v>161.6398507657161</v>
+        <v>246.3401339496097</v>
       </c>
       <c r="D8" t="n">
-        <v>34.71459882216722</v>
+        <v>31.79389940203295</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>65.45311944213483</v>
+        <v>77.76718089650257</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
         <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>22.0343454741154</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.52696183746906</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96750451476862</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.013384614960961</v>
+        <v>1.256637061435917</v>
       </c>
       <c r="C2" t="n">
-        <v>4.519966430352315</v>
+        <v>13.52357462599981</v>
       </c>
       <c r="D2" t="n">
-        <v>11.13694595697582</v>
+        <v>8.594219402976577</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.003248342749</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C3" t="n">
-        <v>13.28304643845934</v>
+        <v>24.27862072602362</v>
       </c>
       <c r="D3" t="n">
-        <v>62.26243940333271</v>
+        <v>57.20643872646164</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.2881604656256</v>
+        <v>19.93536888243573</v>
       </c>
       <c r="C4" t="n">
-        <v>63.86465165666351</v>
+        <v>81.46444275069608</v>
       </c>
       <c r="D4" t="n">
-        <v>154.6203546803514</v>
+        <v>132.2728316885812</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>69.72863069412972</v>
+        <v>38.9508401659922</v>
       </c>
       <c r="C5" t="n">
-        <v>167.4861583445059</v>
+        <v>217.9725340353981</v>
       </c>
       <c r="D5" t="n">
-        <v>171.4867802393116</v>
+        <v>123.1357058051562</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>71.20517924131691</v>
+        <v>41.74096714146165</v>
       </c>
       <c r="C6" t="n">
-        <v>282.7678825156876</v>
+        <v>392.3731414609143</v>
       </c>
       <c r="D6" t="n">
-        <v>105.7813516371854</v>
+        <v>71.88945739117695</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.2133266559246</v>
+        <v>20.84054026575129</v>
       </c>
       <c r="C7" t="n">
-        <v>311.1109387372929</v>
+        <v>442.981253867133</v>
       </c>
       <c r="D7" t="n">
-        <v>56.8323928511436</v>
+        <v>44.67541102945535</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.429686699290613</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>231.2359455197725</v>
+        <v>337.5494044126596</v>
       </c>
       <c r="D8" t="n">
-        <v>37.96909246174539</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>113.7109278443868</v>
+        <v>151.0968621698096</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>47.83074815090461</v>
+        <v>50.39310965898878</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>25.62361508084176</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.07602084605028</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>25.05518316008284</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>12.48783079801943</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.29148125717007</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.091744504851459</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.133558745506572</v>
+        <v>4.344233591292136</v>
       </c>
       <c r="C2" t="n">
-        <v>3.020837685967436</v>
+        <v>13.7729385428785</v>
       </c>
       <c r="D2" t="n">
-        <v>12.311116211255</v>
+        <v>7.389614969865741</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.873575530330414</v>
+        <v>0.9277515805132357</v>
       </c>
       <c r="C2" t="n">
-        <v>2.567270246605409</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="D2" t="n">
-        <v>8.196611582756619</v>
+        <v>6.462845137056753</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.48492661263569</v>
+        <v>7.7410806479861</v>
       </c>
       <c r="C3" t="n">
-        <v>16.5915362017711</v>
+        <v>35.79943003535994</v>
       </c>
       <c r="D3" t="n">
-        <v>67.32825755724626</v>
+        <v>60.88308387886595</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.04186496504667</v>
+        <v>28.89479843139213</v>
       </c>
       <c r="C4" t="n">
-        <v>91.70014431517332</v>
+        <v>120.0461457798915</v>
       </c>
       <c r="D4" t="n">
-        <v>159.4446628990202</v>
+        <v>132.7961032149448</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.04334543436966</v>
+        <v>23.51285751671111</v>
       </c>
       <c r="C5" t="n">
-        <v>244.5042657426682</v>
+        <v>328.517325533589</v>
       </c>
       <c r="D5" t="n">
-        <v>155.0670498857837</v>
+        <v>109.3666942530947</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.85664913964674</v>
+        <v>12.92078153559227</v>
       </c>
       <c r="C6" t="n">
-        <v>260.3477101938032</v>
+        <v>357.15294257106</v>
       </c>
       <c r="D6" t="n">
-        <v>84.36747071215392</v>
+        <v>60.37748381117885</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.228207435741766</v>
+        <v>4.012402867256713</v>
       </c>
       <c r="C7" t="n">
-        <v>162.5921460388355</v>
+        <v>237.3905218776957</v>
       </c>
       <c r="D7" t="n">
-        <v>33.89582123682538</v>
+        <v>29.04500583014188</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>1.335176877775662</v>
       </c>
       <c r="C8" t="n">
-        <v>83.7823490804228</v>
+        <v>111.3203721845458</v>
       </c>
       <c r="D8" t="n">
-        <v>25.03456645829366</v>
+        <v>24.03318379996192</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>36.49843440078366</v>
+        <v>38.38437174064178</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>19.52499834206056</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.92242623583128</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D10" t="n">
-        <v>19.64477156197868</v>
+        <v>18.64829764216817</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.52575910558656</v>
+        <v>14.57109942643116</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>15.99267010218054</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>10.19741340401162</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.14636252339079</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.916592502868027</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.516841260790327</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C2" t="n">
-        <v>7.508406442079605</v>
+        <v>8.285950623843078</v>
       </c>
       <c r="D2" t="n">
-        <v>12.25810183522568</v>
+        <v>7.901105523778329</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.90721699418206</v>
+        <v>9.233337158441252</v>
       </c>
       <c r="C3" t="n">
-        <v>7.608544707912781</v>
+        <v>34.70478134512475</v>
       </c>
       <c r="D3" t="n">
-        <v>13.47939597930871</v>
+        <v>9.341329405908402</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39848878385636</v>
+        <v>13.39762328995897</v>
       </c>
       <c r="C21" t="n">
-        <v>70.1450295154833</v>
+        <v>70.14049840037343</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576292798100748</v>
+        <v>1.576190975289291</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.262167694762903</v>
+        <v>3.913246349127786</v>
       </c>
       <c r="C2" t="n">
-        <v>5.749114556069322</v>
+        <v>11.14676343401828</v>
       </c>
       <c r="D2" t="n">
-        <v>22.48791291347744</v>
+        <v>11.98713946885355</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.84326452468578</v>
+        <v>15.17781950765569</v>
       </c>
       <c r="C3" t="n">
-        <v>21.392282475538</v>
+        <v>33.20761609614836</v>
       </c>
       <c r="D3" t="n">
-        <v>20.51852701875834</v>
+        <v>13.71992416684918</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.74995743505333</v>
+        <v>10.86107485208246</v>
       </c>
       <c r="C4" t="n">
-        <v>12.32878766993144</v>
+        <v>53.42474656970293</v>
       </c>
       <c r="D4" t="n">
-        <v>22.1305567491316</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44367789175205</v>
+        <v>15.43953979361435</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15946613293249</v>
+        <v>86.1363799012169</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251300608789905</v>
+        <v>3.2504294302346</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.080544369477244</v>
+        <v>4.348160582109124</v>
       </c>
       <c r="C2" t="n">
-        <v>4.272566008882119</v>
+        <v>9.599529052125312</v>
       </c>
       <c r="D2" t="n">
-        <v>25.67662945687108</v>
+        <v>12.47899506868121</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.06415775814131</v>
+        <v>14.26479414270615</v>
       </c>
       <c r="C3" t="n">
-        <v>21.98623983660732</v>
+        <v>39.69205968269855</v>
       </c>
       <c r="D3" t="n">
-        <v>33.74757733348411</v>
+        <v>20.12582793705961</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.01493150420873</v>
+        <v>21.3775562599743</v>
       </c>
       <c r="C4" t="n">
-        <v>36.59071868498287</v>
+        <v>70.11838453271569</v>
       </c>
       <c r="D4" t="n">
-        <v>27.43984833369835</v>
+        <v>22.36028571192535</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.53553552490002</v>
+        <v>9.891108120286615</v>
       </c>
       <c r="C5" t="n">
-        <v>15.24163310843173</v>
+        <v>58.53670686571608</v>
       </c>
       <c r="D5" t="n">
-        <v>30.38509144643879</v>
+        <v>29.84513020910304</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>37.30543101367455</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74017182876124</v>
+        <v>16.72944806810197</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1150481554436</v>
+        <v>102.049633215422</v>
       </c>
       <c r="D21" t="n">
-        <v>5.022051548628373</v>
+        <v>4.182362017025493</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.283185307179586</v>
+        <v>4.386448742574749</v>
       </c>
       <c r="C2" t="n">
-        <v>5.886559234663874</v>
+        <v>10.62643715076747</v>
       </c>
       <c r="D2" t="n">
-        <v>30.5951854551476</v>
+        <v>24.03122030455342</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.70581984609123</v>
+        <v>14.5593184539802</v>
       </c>
       <c r="C3" t="n">
-        <v>18.85446466005999</v>
+        <v>38.26361677301944</v>
       </c>
       <c r="D3" t="n">
-        <v>45.7543517564226</v>
+        <v>25.13274122871834</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.31146036862027</v>
+        <v>24.54271085846601</v>
       </c>
       <c r="C4" t="n">
-        <v>46.53287768589032</v>
+        <v>85.44641143912114</v>
       </c>
       <c r="D4" t="n">
-        <v>37.33095645398497</v>
+        <v>27.14630577012855</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.81367322483814</v>
+        <v>20.96031348566941</v>
       </c>
       <c r="C5" t="n">
-        <v>44.00684084286328</v>
+        <v>96.87395471655404</v>
       </c>
       <c r="D5" t="n">
-        <v>33.52668410002858</v>
+        <v>30.90050899116836</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.74719211838983</v>
+        <v>9.620145753914496</v>
       </c>
       <c r="C6" t="n">
-        <v>18.55601335796896</v>
+        <v>53.89696721544566</v>
       </c>
       <c r="D6" t="n">
-        <v>38.40007970390975</v>
+        <v>38.15856976866503</v>
       </c>
     </row>
     <row r="7">
@@ -5521,7 +5521,7 @@
         <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>9.82238578098934</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5588,10 +5588,10 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07031247988807</v>
+        <v>18.0478771498775</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8872766545079</v>
+        <v>117.7409128349151</v>
       </c>
       <c r="D21" t="n">
-        <v>6.883928563766881</v>
+        <v>6.015959049959167</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.219772617031043</v>
+        <v>5.43593703841459</v>
       </c>
       <c r="C2" t="n">
-        <v>7.950192908990671</v>
+        <v>11.80846138668064</v>
       </c>
       <c r="D2" t="n">
-        <v>25.22011677439631</v>
+        <v>21.71920446105219</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.92180434102552</v>
+        <v>13.11614932873739</v>
       </c>
       <c r="C3" t="n">
-        <v>19.87057353395544</v>
+        <v>37.47330987110075</v>
       </c>
       <c r="D3" t="n">
-        <v>55.3411180883927</v>
+        <v>35.55890184781947</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.53445596620454</v>
+        <v>19.10579207234717</v>
       </c>
       <c r="C4" t="n">
-        <v>38.88800831292041</v>
+        <v>76.1168630056637</v>
       </c>
       <c r="D4" t="n">
-        <v>44.27387621841841</v>
+        <v>29.02242563294421</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.57390580082366</v>
+        <v>17.72054606165493</v>
       </c>
       <c r="C5" t="n">
-        <v>49.7746086053133</v>
+        <v>95.03317777109126</v>
       </c>
       <c r="D5" t="n">
-        <v>32.00497515844602</v>
+        <v>27.243498792849</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.27675504160637</v>
+        <v>10.18366893615217</v>
       </c>
       <c r="C6" t="n">
-        <v>30.5510068084565</v>
+        <v>71.20517924131691</v>
       </c>
       <c r="D6" t="n">
-        <v>31.35603992593888</v>
+        <v>30.26924521733767</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.389794896314989</v>
+        <v>5.030475236560656</v>
       </c>
       <c r="C7" t="n">
-        <v>15.57051858935441</v>
+        <v>31.32069700858599</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5972,7 +5972,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.064268110122634</v>
+        <v>7.048858810213058</v>
       </c>
       <c r="C21" t="n">
-        <v>66.2275135323997</v>
+        <v>66.08305134574742</v>
       </c>
       <c r="D21" t="n">
-        <v>5.298201082591976</v>
+        <v>4.405536756383161</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.664684253504096</v>
+        <v>4.406083696659685</v>
       </c>
       <c r="C2" t="n">
-        <v>6.558074664368693</v>
+        <v>7.621307428067988</v>
       </c>
       <c r="D2" t="n">
-        <v>26.72317250959818</v>
+        <v>21.006455627769</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.48202242725196</v>
+        <v>16.77806826557799</v>
       </c>
       <c r="C3" t="n">
-        <v>27.21895510024282</v>
+        <v>42.95146206079795</v>
       </c>
       <c r="D3" t="n">
-        <v>63.63197745075702</v>
+        <v>45.20948178056562</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.6560538128109</v>
+        <v>22.94737083906494</v>
       </c>
       <c r="C4" t="n">
-        <v>45.92026711844031</v>
+        <v>87.20766682053993</v>
       </c>
       <c r="D4" t="n">
-        <v>63.95399069774997</v>
+        <v>40.91728081759857</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.01693605734623</v>
+        <v>24.15099352447154</v>
       </c>
       <c r="C5" t="n">
-        <v>63.61725123519332</v>
+        <v>122.6202882604266</v>
       </c>
       <c r="D5" t="n">
-        <v>41.72427743048944</v>
+        <v>31.63681976935347</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.21891404251382</v>
+        <v>17.87173520810894</v>
       </c>
       <c r="C6" t="n">
-        <v>59.57245069369646</v>
+        <v>117.4543318406799</v>
       </c>
       <c r="D6" t="n">
-        <v>34.65667570761666</v>
+        <v>32.60384125803657</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.71970318267092</v>
+        <v>9.102764713776425</v>
       </c>
       <c r="C7" t="n">
-        <v>32.5184292077671</v>
+        <v>72.22325161062085</v>
       </c>
       <c r="D7" t="n">
         <v>33.47661496711198</v>
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>20.11110172149591</v>
+        <v>31.62700229231099</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
         <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -6193,10 +6193,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.289418351841991</v>
+        <v>7.265169685733696</v>
       </c>
       <c r="C21" t="n">
-        <v>76.53889269434092</v>
+        <v>75.3761354894871</v>
       </c>
       <c r="D21" t="n">
-        <v>6.378241057861743</v>
+        <v>5.448877264300272</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.187554869240146</v>
+        <v>3.51171153809084</v>
       </c>
       <c r="C2" t="n">
-        <v>8.24275372485622</v>
+        <v>6.163412087261475</v>
       </c>
       <c r="D2" t="n">
-        <v>20.99369290761379</v>
+        <v>25.16023016443726</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.90631736193583</v>
+        <v>15.85522542358599</v>
       </c>
       <c r="C3" t="n">
-        <v>26.18812001078367</v>
+        <v>35.1023891653447</v>
       </c>
       <c r="D3" t="n">
-        <v>70.24404823885929</v>
+        <v>51.11960296013142</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.47960126795373</v>
+        <v>28.01417074068274</v>
       </c>
       <c r="C4" t="n">
-        <v>59.27007240078844</v>
+        <v>98.77069128115886</v>
       </c>
       <c r="D4" t="n">
-        <v>80.87735762355649</v>
+        <v>53.24606848753</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.80357801035519</v>
+        <v>29.77149913128453</v>
       </c>
       <c r="C5" t="n">
-        <v>76.03635969391547</v>
+        <v>143.8751260573701</v>
       </c>
       <c r="D5" t="n">
-        <v>56.05779391249288</v>
+        <v>39.24536447726625</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.6440929139107</v>
+        <v>25.47929816831747</v>
       </c>
       <c r="C6" t="n">
-        <v>82.91841110068562</v>
+        <v>157.5449810913027</v>
       </c>
       <c r="D6" t="n">
-        <v>40.29190752999335</v>
+        <v>35.13969557810609</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.28348840681585</v>
+        <v>15.51063197939536</v>
       </c>
       <c r="C7" t="n">
-        <v>61.86286808770426</v>
+        <v>124.3844888849581</v>
       </c>
       <c r="D7" t="n">
-        <v>35.99185258539232</v>
+        <v>35.75230614555609</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.095892479846697</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>33.12907627980861</v>
+        <v>65.42366701100744</v>
       </c>
       <c r="D8" t="n">
-        <v>34.54770171244525</v>
+        <v>33.46287049925253</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>24.96093538047515</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
         <v>31.73990327829938</v>
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.50230510133364</v>
+        <v>7.466297652196379</v>
       </c>
       <c r="C21" t="n">
-        <v>86.27650866533686</v>
+        <v>83.99584858720925</v>
       </c>
       <c r="D21" t="n">
-        <v>7.50230510133364</v>
+        <v>6.533010445671831</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_8_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_8_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497626464536</v>
+        <v>10.84497645299279</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907170646444</v>
+        <v>37.78907236275674</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.572579895754143</v>
+        <v>6.393141050055229</v>
       </c>
       <c r="C2" t="n">
-        <v>17.2689421177014</v>
+        <v>5.662720758095602</v>
       </c>
       <c r="D2" t="n">
-        <v>31.32069700858599</v>
+        <v>23.52071149834508</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.73955912093411</v>
+        <v>18.89373456822987</v>
       </c>
       <c r="C3" t="n">
-        <v>28.99100970640831</v>
+        <v>31.38156536624929</v>
       </c>
       <c r="D3" t="n">
-        <v>58.35508354043041</v>
+        <v>59.51845456996288</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.94584931201296</v>
+        <v>37.54792269662352</v>
       </c>
       <c r="C4" t="n">
-        <v>92.96365361053896</v>
+        <v>65.08987279156354</v>
       </c>
       <c r="D4" t="n">
-        <v>65.38341535513332</v>
+        <v>78.56730527546374</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.76016012719008</v>
+        <v>48.30198704894308</v>
       </c>
       <c r="C5" t="n">
-        <v>161.595672119025</v>
+        <v>108.11496593018</v>
       </c>
       <c r="D5" t="n">
-        <v>47.95837535245669</v>
+        <v>57.55495916146927</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.40258297866598</v>
+        <v>44.47807974090175</v>
       </c>
       <c r="C6" t="n">
-        <v>192.8054316370311</v>
+        <v>113.9121861237574</v>
       </c>
       <c r="D6" t="n">
-        <v>39.40637110076273</v>
+        <v>43.14977509705582</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.51736534460484</v>
+        <v>30.06307819944583</v>
       </c>
       <c r="C7" t="n">
-        <v>173.7310554912198</v>
+        <v>91.0875337477233</v>
       </c>
       <c r="D7" t="n">
-        <v>37.96811071404115</v>
+        <v>38.74663664350886</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.10004045484194</v>
+        <v>15.43798264928109</v>
       </c>
       <c r="C8" t="n">
-        <v>113.9907259400971</v>
+        <v>54.24156065963627</v>
       </c>
       <c r="D8" t="n">
-        <v>35.13184159647211</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>55.24687030878498</v>
+        <v>32.72655972106742</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>34.50155957034565</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>26.90381408717959</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>24.97566159603886</v>
+        <v>26.01631416254048</v>
       </c>
       <c r="D13" t="n">
         <v>32.5203927031756</v>
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>22.73924032576462</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.650892531366663</v>
+        <v>7.715706076253899</v>
       </c>
       <c r="C21" t="n">
-        <v>92.76707194282079</v>
+        <v>96.44632595317374</v>
       </c>
       <c r="D21" t="n">
-        <v>7.650892531366663</v>
+        <v>8.680169335785637</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.062872910800801</v>
+        <v>9.504299524813371</v>
       </c>
       <c r="C2" t="n">
-        <v>11.66119923104361</v>
+        <v>8.565748719553421</v>
       </c>
       <c r="D2" t="n">
-        <v>33.07802539918778</v>
+        <v>26.61223501901829</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.7136327699962</v>
+        <v>20.17000658375072</v>
       </c>
       <c r="C3" t="n">
-        <v>47.21224709722911</v>
+        <v>26.31083847381452</v>
       </c>
       <c r="D3" t="n">
-        <v>67.1024555852695</v>
+        <v>63.41599295582272</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.15906849028376</v>
+        <v>36.87149852839745</v>
       </c>
       <c r="C4" t="n">
-        <v>83.08530821040756</v>
+        <v>71.1904530257532</v>
       </c>
       <c r="D4" t="n">
-        <v>76.65289725218247</v>
+        <v>87.84580282830034</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.14718970684157</v>
+        <v>51.98354093986863</v>
       </c>
       <c r="C5" t="n">
-        <v>164.0991287648544</v>
+        <v>114.029995848267</v>
       </c>
       <c r="D5" t="n">
-        <v>57.23589115758906</v>
+        <v>71.05399009486291</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.96360288614742</v>
+        <v>54.33973543006097</v>
       </c>
       <c r="C6" t="n">
-        <v>219.6130344491945</v>
+        <v>140.8405439035432</v>
       </c>
       <c r="D6" t="n">
-        <v>44.51833139677587</v>
+        <v>49.99255659565609</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.2845522699781</v>
+        <v>41.32176087174825</v>
       </c>
       <c r="C7" t="n">
-        <v>221.2810237987098</v>
+        <v>127.1392729430747</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>42.33983324105218</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.27385085622263</v>
+        <v>23.44904391593506</v>
       </c>
       <c r="C8" t="n">
-        <v>164.2267559664064</v>
+        <v>85.70166584222531</v>
       </c>
       <c r="D8" t="n">
-        <v>37.1346069131356</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.985936736971052</v>
+        <v>11.31562403914873</v>
       </c>
       <c r="C9" t="n">
-        <v>92.96561710594743</v>
+        <v>49.58905828921062</v>
       </c>
       <c r="D9" t="n">
-        <v>34.61249706092553</v>
+        <v>36.16562192904399</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.836490101747287</v>
+        <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>46.54956739686252</v>
+        <v>34.16482010778901</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.94134148411922</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>27.0569667290421</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.817459102982864</v>
+        <v>7.902338218597078</v>
       </c>
       <c r="C21" t="n">
-        <v>100.6497859509044</v>
+        <v>105.6937736737359</v>
       </c>
       <c r="D21" t="n">
-        <v>8.794641490855721</v>
+        <v>9.877922773246347</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.946044933995431</v>
+        <v>11.71617710248144</v>
       </c>
       <c r="C2" t="n">
-        <v>12.73130422867264</v>
+        <v>7.903069019186824</v>
       </c>
       <c r="D2" t="n">
-        <v>29.67725135167683</v>
+        <v>20.53718022513903</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.1273494641116</v>
+        <v>25.30945581548277</v>
       </c>
       <c r="C3" t="n">
-        <v>45.87707021945345</v>
+        <v>29.48679229705295</v>
       </c>
       <c r="D3" t="n">
-        <v>73.92069339126358</v>
+        <v>68.16765184437729</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.1170332654504</v>
+        <v>36.89702396870788</v>
       </c>
       <c r="C4" t="n">
-        <v>96.54997797415255</v>
+        <v>68.44646819238336</v>
       </c>
       <c r="D4" t="n">
-        <v>86.722683454642</v>
+        <v>96.99667317958487</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.34353924769093</v>
+        <v>53.21072557017713</v>
       </c>
       <c r="C5" t="n">
-        <v>158.9694970101648</v>
+        <v>120.4358996184775</v>
       </c>
       <c r="D5" t="n">
-        <v>67.59332943739291</v>
+        <v>82.29500130848889</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.03531152628644</v>
+        <v>61.7460401108989</v>
       </c>
       <c r="C6" t="n">
-        <v>234.1841338756257</v>
+        <v>157.665736058925</v>
       </c>
       <c r="D6" t="n">
-        <v>49.67054334866313</v>
+        <v>58.88817254383644</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.75230614555609</v>
+        <v>51.3228247349105</v>
       </c>
       <c r="C7" t="n">
-        <v>258.2909487534061</v>
+        <v>161.7537334994087</v>
       </c>
       <c r="D7" t="n">
-        <v>42.51949307092936</v>
+        <v>45.87314322863646</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.94835258676919</v>
+        <v>32.54493639578176</v>
       </c>
       <c r="C8" t="n">
-        <v>214.7965802121596</v>
+        <v>121.5010958775852</v>
       </c>
       <c r="D8" t="n">
-        <v>39.05392367493811</v>
+        <v>40.80634332701867</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.09218647320796</v>
+        <v>16.52968609640354</v>
       </c>
       <c r="C9" t="n">
-        <v>137.1187383567435</v>
+        <v>74.77186865084555</v>
       </c>
       <c r="D9" t="n">
-        <v>35.61093447614454</v>
+        <v>37.27499683484289</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.8329640215578</v>
+        <v>8.398851609831464</v>
       </c>
       <c r="C10" t="n">
-        <v>70.18023463808325</v>
+        <v>44.69897297435728</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>36.15776794741003</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>40.69246059332603</v>
+        <v>35.7169632282032</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>37.31623023842126</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.82120841130262</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>26.42668470291564</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>20.30548776693678</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>19.26188995732242</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>19.25796296650543</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.966450390462477</v>
+        <v>8.072979141733866</v>
       </c>
       <c r="C21" t="n">
-        <v>107.5470802712434</v>
+        <v>114.0308303769908</v>
       </c>
       <c r="D21" t="n">
-        <v>9.958062988078096</v>
+        <v>11.10034631988406</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.659374604355362</v>
+        <v>10.41830663746715</v>
       </c>
       <c r="C2" t="n">
-        <v>9.064476553310801</v>
+        <v>5.310273332270997</v>
       </c>
       <c r="D2" t="n">
-        <v>24.5927799913826</v>
+        <v>16.78886749032471</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.77315952705676</v>
+        <v>28.47559216167874</v>
       </c>
       <c r="C3" t="n">
-        <v>66.04216806468294</v>
+        <v>43.72213400863171</v>
       </c>
       <c r="D3" t="n">
-        <v>77.26845306274521</v>
+        <v>74.74536146283091</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18.90158854986384</v>
+        <v>25.56372847088269</v>
       </c>
       <c r="C4" t="n">
-        <v>129.4012196536594</v>
+        <v>98.88555576255573</v>
       </c>
       <c r="D4" t="n">
-        <v>80.40513697781377</v>
+        <v>93.41034881597128</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.78912953223197</v>
+        <v>34.77841242294326</v>
       </c>
       <c r="C5" t="n">
-        <v>139.9235915477767</v>
+        <v>94.19869222248147</v>
       </c>
       <c r="D5" t="n">
-        <v>47.19752088166541</v>
+        <v>58.09492039880502</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.1786623866397</v>
+        <v>31.83905979642831</v>
       </c>
       <c r="C6" t="n">
-        <v>170.1034977240279</v>
+        <v>106.5058814429195</v>
       </c>
       <c r="D6" t="n">
-        <v>27.97490083251287</v>
+        <v>30.18874190558942</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.21119892960008</v>
+        <v>21.55917958525995</v>
       </c>
       <c r="C7" t="n">
-        <v>151.0340303167378</v>
+        <v>85.39830580161305</v>
       </c>
       <c r="D7" t="n">
-        <v>27.42806736124739</v>
+        <v>28.68568617038755</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.344855486097888</v>
+        <v>11.43245201595411</v>
       </c>
       <c r="C8" t="n">
-        <v>101.0561999366454</v>
+        <v>55.07604620824605</v>
       </c>
       <c r="D8" t="n">
-        <v>26.20284622634736</v>
+        <v>27.45457454926205</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>53.58280795008665</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.5124976638126</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>27.90126975469435</v>
       </c>
       <c r="D10" t="n">
-        <v>28.18597658892593</v>
+        <v>29.18245050873644</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.25371718051895</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>27.55471281509523</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.27567548291088</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>18.63357142660446</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>23.29196428325557</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
         <v>20.25247339090745</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>17.9443845382232</v>
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>16.58662746324986</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>14.44641746799181</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>9.628981483252716</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.831360379047801</v>
+        <v>6.027930904075415</v>
       </c>
       <c r="C2" t="n">
-        <v>4.23525959612074</v>
+        <v>2.980586030093316</v>
       </c>
       <c r="D2" t="n">
-        <v>17.92376783643402</v>
+        <v>11.31955102996572</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.79770321966292</v>
+        <v>32.85418692261951</v>
       </c>
       <c r="C3" t="n">
-        <v>51.99826715543232</v>
+        <v>32.24059460746525</v>
       </c>
       <c r="D3" t="n">
-        <v>78.79016200432777</v>
+        <v>72.35971454151115</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.28745645536184</v>
+        <v>38.18605870438394</v>
       </c>
       <c r="C4" t="n">
-        <v>150.3576061485118</v>
+        <v>107.71735810996</v>
       </c>
       <c r="D4" t="n">
-        <v>96.84352053772237</v>
+        <v>107.8577480316673</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.4889357189107</v>
+        <v>38.50905369908114</v>
       </c>
       <c r="C5" t="n">
-        <v>185.5503161026472</v>
+        <v>137.2728727463103</v>
       </c>
       <c r="D5" t="n">
-        <v>59.02758071783948</v>
+        <v>72.60024272905164</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.84156307118455</v>
+        <v>38.11831811279092</v>
       </c>
       <c r="C6" t="n">
-        <v>197.7161336536737</v>
+        <v>128.966305420678</v>
       </c>
       <c r="D6" t="n">
-        <v>32.72459622565894</v>
+        <v>36.95102009244145</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.19312656029614</v>
+        <v>20.4213339960379</v>
       </c>
       <c r="C7" t="n">
-        <v>189.2416874706151</v>
+        <v>113.6048990923282</v>
       </c>
       <c r="D7" t="n">
-        <v>29.8235317596096</v>
+        <v>31.20092378866788</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.093127163183205</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>130.8473340220149</v>
+        <v>73.76852249710534</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>28.37250865273282</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.104687151455913</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>55.80155776168444</v>
+        <v>40.71405904281946</v>
       </c>
       <c r="D9" t="n">
-        <v>28.06718511671205</v>
+        <v>28.84374755077128</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>29.46715734296802</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2150,10 +2150,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>30.03068052520567</v>
       </c>
       <c r="D11" t="n">
         <v>29.49759152179966</v>
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>27.77167905773377</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>14.69185439405351</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>12.27773678931061</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>8.025787482217675</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.510328879759094</v>
+        <v>6.495242811296897</v>
       </c>
       <c r="C2" t="n">
-        <v>6.33423618780042</v>
+        <v>6.975317438673588</v>
       </c>
       <c r="D2" t="n">
-        <v>17.67734916266807</v>
+        <v>10.39376294486098</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.25850274585317</v>
+        <v>26.56118413839745</v>
       </c>
       <c r="C3" t="n">
-        <v>34.25808613969245</v>
+        <v>20.86213871524472</v>
       </c>
       <c r="D3" t="n">
-        <v>75.00552460445631</v>
+        <v>65.10950774564847</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.74615361742335</v>
+        <v>50.80838893788518</v>
       </c>
       <c r="C4" t="n">
-        <v>140.2367690654314</v>
+        <v>94.3420273873015</v>
       </c>
       <c r="D4" t="n">
-        <v>110.4868683836403</v>
+        <v>118.4508057604904</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.34229545807943</v>
+        <v>47.44295780772712</v>
       </c>
       <c r="C5" t="n">
-        <v>227.4218556887737</v>
+        <v>167.9524885040231</v>
       </c>
       <c r="D5" t="n">
-        <v>75.54548584179207</v>
+        <v>92.38245896962486</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.43025184083414</v>
+        <v>44.80009298789471</v>
       </c>
       <c r="C6" t="n">
-        <v>242.8382398885614</v>
+        <v>173.2431268822092</v>
       </c>
       <c r="D6" t="n">
-        <v>40.89568236810514</v>
+        <v>49.06676851055134</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.36144738607885</v>
+        <v>31.02126395879071</v>
       </c>
       <c r="C7" t="n">
-        <v>231.2820876618721</v>
+        <v>149.1775454080071</v>
       </c>
       <c r="D7" t="n">
-        <v>31.91956310817654</v>
+        <v>34.37491411649782</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.846929473595507</v>
+        <v>14.52004854581032</v>
       </c>
       <c r="C8" t="n">
-        <v>182.8357837004047</v>
+        <v>109.2341583130213</v>
       </c>
       <c r="D8" t="n">
-        <v>28.37250865273282</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>6.434374453633594</v>
       </c>
       <c r="C9" t="n">
-        <v>98.51249163494191</v>
+        <v>63.01249464937726</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>29.50937249425062</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>45.69544689416779</v>
+        <v>39.28954312395736</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.89069151412589</v>
       </c>
     </row>
     <row r="11">
@@ -2461,10 +2461,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
         <v>30.03068052520567</v>
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>26.25291535926396</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.21141991377833</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>20.28094407433061</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>15.29268398905256</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>15.11106066376691</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.533489914033518</v>
+        <v>3.803290606252143</v>
       </c>
       <c r="C2" t="n">
-        <v>3.129811681138832</v>
+        <v>3.189698291097887</v>
       </c>
       <c r="D2" t="n">
-        <v>12.47212283475148</v>
+        <v>7.176575718044184</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.65963664626262</v>
+        <v>27.02751429791469</v>
       </c>
       <c r="C3" t="n">
-        <v>32.56948008838793</v>
+        <v>25.01493150420873</v>
       </c>
       <c r="D3" t="n">
-        <v>74.72572650874598</v>
+        <v>62.07099860100459</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.32422308877548</v>
+        <v>56.43674852633215</v>
       </c>
       <c r="C4" t="n">
-        <v>135.5528507684698</v>
+        <v>87.96066730969723</v>
       </c>
       <c r="D4" t="n">
-        <v>119.6760268953904</v>
+        <v>125.4064882450791</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.39767424014475</v>
+        <v>49.38190952361457</v>
       </c>
       <c r="C5" t="n">
-        <v>276.190172897234</v>
+        <v>194.1406085148068</v>
       </c>
       <c r="D5" t="n">
-        <v>78.0734861802276</v>
+        <v>100.3591590666302</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.15099352447154</v>
+        <v>37.8768081775462</v>
       </c>
       <c r="C6" t="n">
-        <v>277.0118957256886</v>
+        <v>211.9249681772378</v>
       </c>
       <c r="D6" t="n">
-        <v>40.73467574460867</v>
+        <v>48.70450360768427</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.527640485537042</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>239.905759495976</v>
+        <v>153.0701750553457</v>
       </c>
       <c r="D7" t="n">
-        <v>32.09922293805371</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.421390749300134</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>122.7528242004999</v>
+        <v>80.69475255056658</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>34.83437204208531</v>
+        <v>29.95312245657017</v>
       </c>
       <c r="D9" t="n">
-        <v>30.95155987178918</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -2758,10 +2758,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
         <v>23.48831382410494</v>
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>19.19120412261664</v>
+        <v>20.96816746730337</v>
       </c>
       <c r="D11" t="n">
-        <v>22.56743447752142</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.75370449942107</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>12.81278928812512</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>9.919578803709772</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>6.138868394655306</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.443169125242811</v>
+        <v>4.275511251994859</v>
       </c>
       <c r="C2" t="n">
-        <v>8.107272541670159</v>
+        <v>7.118652603493622</v>
       </c>
       <c r="D2" t="n">
-        <v>10.14930776650353</v>
+        <v>12.40143700004571</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.184249773228911</v>
+        <v>20.20436775339936</v>
       </c>
       <c r="C3" t="n">
-        <v>22.76672926148353</v>
+        <v>18.51085296357361</v>
       </c>
       <c r="D3" t="n">
-        <v>68.95795874629596</v>
+        <v>54.33482669153972</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.68234001664731</v>
+        <v>54.22879793948106</v>
       </c>
       <c r="C4" t="n">
-        <v>110.2571394208465</v>
+        <v>75.12137083355744</v>
       </c>
       <c r="D4" t="n">
-        <v>126.7720993016864</v>
+        <v>127.4612861900676</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.65002445786519</v>
+        <v>64.77080478768333</v>
       </c>
       <c r="C5" t="n">
-        <v>266.5445017030091</v>
+        <v>180.4452280405638</v>
       </c>
       <c r="D5" t="n">
-        <v>96.13764393836894</v>
+        <v>118.9141906768949</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.95352336719769</v>
+        <v>49.87180162803373</v>
       </c>
       <c r="C6" t="n">
-        <v>346.5667570761666</v>
+        <v>257.9728624972302</v>
       </c>
       <c r="D6" t="n">
-        <v>51.07935130425731</v>
+        <v>65.20768251607315</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.1750541909922</v>
+        <v>21.43940636534185</v>
       </c>
       <c r="C7" t="n">
-        <v>308.5957011190126</v>
+        <v>222.7781890476862</v>
       </c>
       <c r="D7" t="n">
-        <v>35.39298648580176</v>
+        <v>39.16584291322225</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.339324852770902</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>195.5199640392735</v>
+        <v>131.5983710157637</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>73.55155625446676</v>
+        <v>56.57812019574367</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>24.34243432679967</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>22.56743447752142</v>
+        <v>24.52209415667683</v>
       </c>
       <c r="D11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.91359050649305</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.30897278939726</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>14.44249047717483</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>24.38563122578652</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9198975988792613</v>
+        <v>3.145519644406781</v>
       </c>
       <c r="C2" t="n">
-        <v>5.496805396077892</v>
+        <v>3.726714285320892</v>
       </c>
       <c r="D2" t="n">
-        <v>8.875980994095412</v>
+        <v>8.823948365770333</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7.53491363009427</v>
+        <v>18.02979658849267</v>
       </c>
       <c r="C3" t="n">
-        <v>26.94897448157494</v>
+        <v>23.2232419439583</v>
       </c>
       <c r="D3" t="n">
-        <v>63.27363953870693</v>
+        <v>52.29770020522759</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.55547357862122</v>
+        <v>49.44277788127786</v>
       </c>
       <c r="C4" t="n">
-        <v>92.01921231905354</v>
+        <v>63.8518889365083</v>
       </c>
       <c r="D4" t="n">
-        <v>131.9027128040802</v>
+        <v>126.6572348202895</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.37437433715008</v>
+        <v>71.8884756434727</v>
       </c>
       <c r="C5" t="n">
-        <v>250.8610821276663</v>
+        <v>170.1368771459722</v>
       </c>
       <c r="D5" t="n">
-        <v>108.3113154710294</v>
+        <v>132.1186972990145</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.09944392223197</v>
+        <v>60.25672884355649</v>
       </c>
       <c r="C6" t="n">
-        <v>386.5769030150411</v>
+        <v>280.7955513778558</v>
       </c>
       <c r="D6" t="n">
-        <v>59.65295400544471</v>
+        <v>76.88066271956774</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.73777555197486</v>
+        <v>20.12190094624263</v>
       </c>
       <c r="C7" t="n">
-        <v>374.2314256341374</v>
+        <v>278.9518291892802</v>
       </c>
       <c r="D7" t="n">
-        <v>39.28561613314036</v>
+        <v>43.77711188006952</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.504839304161113</v>
+        <v>5.006913291658733</v>
       </c>
       <c r="C8" t="n">
-        <v>246.3401339496097</v>
+        <v>174.5743767691678</v>
       </c>
       <c r="D8" t="n">
-        <v>31.79389940203295</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>77.76718089650257</v>
+        <v>68.33749419721195</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.0343454741154</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>19.52696183746906</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.96750451476862</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>7.525096153051802</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.256637061435917</v>
+        <v>5.532148313430777</v>
       </c>
       <c r="C2" t="n">
-        <v>13.52357462599981</v>
+        <v>10.05604173460008</v>
       </c>
       <c r="D2" t="n">
-        <v>8.594219402976577</v>
+        <v>9.690831588620265</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5.551783267515713</v>
+        <v>14.45623494503428</v>
       </c>
       <c r="C3" t="n">
-        <v>24.27862072602362</v>
+        <v>19.1146278016854</v>
       </c>
       <c r="D3" t="n">
-        <v>57.20643872646164</v>
+        <v>47.96819282949916</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.93536888243573</v>
+        <v>42.57643443777567</v>
       </c>
       <c r="C4" t="n">
-        <v>81.46444275069608</v>
+        <v>61.01856506205201</v>
       </c>
       <c r="D4" t="n">
-        <v>132.2728316885812</v>
+        <v>124.1429789497134</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.9508401659922</v>
+        <v>72.69841749947632</v>
       </c>
       <c r="C5" t="n">
-        <v>217.9725340353981</v>
+        <v>147.041262403566</v>
       </c>
       <c r="D5" t="n">
-        <v>123.1357058051562</v>
+        <v>141.7889121858456</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.74096714146165</v>
+        <v>74.38506005537235</v>
       </c>
       <c r="C6" t="n">
-        <v>392.3731414609143</v>
+        <v>277.6559222196745</v>
       </c>
       <c r="D6" t="n">
-        <v>71.88945739117695</v>
+        <v>94.63164296005432</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.84054026575129</v>
+        <v>37.72856427420492</v>
       </c>
       <c r="C7" t="n">
-        <v>442.981253867133</v>
+        <v>331.8915923930852</v>
       </c>
       <c r="D7" t="n">
-        <v>44.67541102945535</v>
+        <v>52.28101049425539</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C8" t="n">
-        <v>337.5494044126596</v>
+        <v>253.8505038870977</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>151.0968621698096</v>
+        <v>123.473427015417</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>34.50155957034565</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>50.39310965898878</v>
+        <v>49.11192890494669</v>
       </c>
       <c r="D10" t="n">
-        <v>25.62361508084176</v>
+        <v>26.90479583488384</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.48783079801943</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>12.29148125717007</v>
+      </c>
+      <c r="D14" t="n">
         <v>11.67690719431156</v>
-      </c>
-      <c r="D14" t="n">
-        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>7.166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.03889435973815</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.344233591292136</v>
+        <v>4.881249585515142</v>
       </c>
       <c r="C2" t="n">
-        <v>13.7729385428785</v>
+        <v>2.916772429317273</v>
       </c>
       <c r="D2" t="n">
-        <v>7.389614969865741</v>
+        <v>6.90364985626357</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9277515805132357</v>
+        <v>3.914228096832033</v>
       </c>
       <c r="C2" t="n">
-        <v>8.114144775599888</v>
+        <v>5.711808143307943</v>
       </c>
       <c r="D2" t="n">
-        <v>6.462845137056753</v>
+        <v>7.132397071353077</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7.7410806479861</v>
+        <v>20.13073667558085</v>
       </c>
       <c r="C3" t="n">
-        <v>35.79943003535994</v>
+        <v>27.9945357865978</v>
       </c>
       <c r="D3" t="n">
-        <v>60.88308387886595</v>
+        <v>52.3566050674824</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.89479843139213</v>
+        <v>56.73029108990194</v>
       </c>
       <c r="C4" t="n">
-        <v>120.0461457798915</v>
+        <v>87.30976858178158</v>
       </c>
       <c r="D4" t="n">
-        <v>132.7961032149448</v>
+        <v>127.8186423544135</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.51285751671111</v>
+        <v>43.9086660724386</v>
       </c>
       <c r="C5" t="n">
-        <v>328.517325533589</v>
+        <v>227.0537002996811</v>
       </c>
       <c r="D5" t="n">
-        <v>109.3666942530947</v>
+        <v>131.7014545247096</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.92078153559227</v>
+        <v>23.42646371873739</v>
       </c>
       <c r="C6" t="n">
-        <v>357.15294257106</v>
+        <v>275.7238427377167</v>
       </c>
       <c r="D6" t="n">
-        <v>60.37748381117885</v>
+        <v>76.31713953733006</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.012402867256713</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>237.3905218776957</v>
+        <v>178.5219842879443</v>
       </c>
       <c r="D7" t="n">
-        <v>29.04500583014188</v>
+        <v>33.65627479698915</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.335176877775662</v>
+        <v>1.919316761802514</v>
       </c>
       <c r="C8" t="n">
-        <v>111.3203721845458</v>
+        <v>90.95892479846698</v>
       </c>
       <c r="D8" t="n">
-        <v>24.03318379996192</v>
+        <v>25.36836067773758</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>38.38437174064178</v>
+        <v>37.49687181600267</v>
       </c>
       <c r="D9" t="n">
-        <v>19.52499834206056</v>
+        <v>20.52343575727956</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.78359889890498</v>
+        <v>22.49183990429443</v>
       </c>
       <c r="D10" t="n">
-        <v>18.64829764216817</v>
+        <v>19.07535789351553</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.57109942643116</v>
+        <v>16.8811517745239</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.8811517745239</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.19741340401162</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>10.14636252339079</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.626036240139976</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>5.838453597155781</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.551783267515713</v>
+        <v>6.376451339083034</v>
       </c>
       <c r="C2" t="n">
-        <v>8.285950623843078</v>
+        <v>5.597925409615312</v>
       </c>
       <c r="D2" t="n">
-        <v>7.901105523778329</v>
+        <v>8.943721585688444</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.233337158441252</v>
+        <v>10.37216449536755</v>
       </c>
       <c r="C3" t="n">
-        <v>34.70478134512475</v>
+        <v>7.466191290796992</v>
       </c>
       <c r="D3" t="n">
-        <v>9.341329405908402</v>
+        <v>9.208793465835081</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>24.19517217116264</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39762328995897</v>
+        <v>13.39948063089694</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14049840037343</v>
+        <v>70.15022212646045</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576190975289291</v>
+        <v>1.576409485987875</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.913246349127786</v>
+        <v>5.819800390775092</v>
       </c>
       <c r="C2" t="n">
-        <v>11.14676343401828</v>
+        <v>6.699446333780234</v>
       </c>
       <c r="D2" t="n">
-        <v>11.98713946885355</v>
+        <v>20.52539925268806</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.17781950765569</v>
+        <v>17.59291886010284</v>
       </c>
       <c r="C3" t="n">
-        <v>33.20761609614836</v>
+        <v>16.6062624173348</v>
       </c>
       <c r="D3" t="n">
-        <v>13.71992416684918</v>
+        <v>14.49550485320416</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.86107485208246</v>
+        <v>12.13734686760332</v>
       </c>
       <c r="C4" t="n">
-        <v>53.42474656970293</v>
+        <v>12.1118214272929</v>
       </c>
       <c r="D4" t="n">
-        <v>19.96089432274615</v>
+        <v>19.89708072197011</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>25.36836067773758</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4924,7 +4924,7 @@
         <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.84843530511426</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5008,7 +5008,7 @@
         <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>26.87534340375643</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43953979361435</v>
+        <v>15.44683123740853</v>
       </c>
       <c r="C21" t="n">
-        <v>86.1363799012169</v>
+        <v>86.17705848238441</v>
       </c>
       <c r="D21" t="n">
-        <v>3.2504294302346</v>
+        <v>3.251964471033374</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.348160582109124</v>
+        <v>5.16791991515521</v>
       </c>
       <c r="C2" t="n">
-        <v>9.599529052125312</v>
+        <v>5.65093978564464</v>
       </c>
       <c r="D2" t="n">
-        <v>12.47899506868121</v>
+        <v>19.22458354456104</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.26479414270615</v>
+        <v>19.1293540172491</v>
       </c>
       <c r="C3" t="n">
-        <v>39.69205968269855</v>
+        <v>22.61455836732528</v>
       </c>
       <c r="D3" t="n">
-        <v>20.12582793705961</v>
+        <v>27.55274931968674</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.3775562599743</v>
+        <v>24.86177886234622</v>
       </c>
       <c r="C4" t="n">
-        <v>70.11838453271569</v>
+        <v>29.32873091666921</v>
       </c>
       <c r="D4" t="n">
-        <v>22.36028571192535</v>
+        <v>22.51343835378785</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.891108120286615</v>
+        <v>11.06920536538279</v>
       </c>
       <c r="C5" t="n">
-        <v>58.53670686571608</v>
+        <v>15.24163310843173</v>
       </c>
       <c r="D5" t="n">
-        <v>29.84513020910304</v>
+        <v>29.96784867213389</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.876741757621407</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>31.67707142522758</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5288,7 +5288,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
         <v>30.17892442854696</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.95035713990669</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72944806810197</v>
+        <v>16.74652418251343</v>
       </c>
       <c r="C21" t="n">
-        <v>102.049633215422</v>
+        <v>102.153797513332</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182362017025493</v>
+        <v>5.023957254754031</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.386448742574749</v>
+        <v>5.658793767278616</v>
       </c>
       <c r="C2" t="n">
-        <v>10.62643715076747</v>
+        <v>8.353691215436109</v>
       </c>
       <c r="D2" t="n">
-        <v>24.03122030455342</v>
+        <v>19.57997621349838</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.5593184539802</v>
+        <v>18.55994034878595</v>
       </c>
       <c r="C3" t="n">
-        <v>38.26361677301944</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D3" t="n">
-        <v>25.13274122871834</v>
+        <v>36.03504948437918</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.54271085846601</v>
+        <v>31.34524070119216</v>
       </c>
       <c r="C4" t="n">
-        <v>85.44641143912114</v>
+        <v>44.83543590524759</v>
       </c>
       <c r="D4" t="n">
-        <v>27.14630577012855</v>
+        <v>30.56671477172444</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.96031348566941</v>
+        <v>24.44551783574558</v>
       </c>
       <c r="C5" t="n">
-        <v>96.87395471655404</v>
+        <v>36.49647090537518</v>
       </c>
       <c r="D5" t="n">
-        <v>30.90050899116836</v>
+        <v>31.46501392111028</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.620145753914496</v>
+        <v>10.465430527271</v>
       </c>
       <c r="C6" t="n">
-        <v>53.89696721544566</v>
+        <v>18.67676832559133</v>
       </c>
       <c r="D6" t="n">
-        <v>38.15856976866503</v>
+        <v>37.91705983342032</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.93176068678823</v>
       </c>
       <c r="C8" t="n">
         <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>33.83593462686631</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.82238578098934</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.06370009425158</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5599,10 +5599,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.58536797810513</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.0478771498775</v>
+        <v>18.08183501354747</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7409128349151</v>
+        <v>117.9624474693335</v>
       </c>
       <c r="D21" t="n">
-        <v>6.015959049959167</v>
+        <v>6.888318100399035</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.43593703841459</v>
+        <v>7.10392638792992</v>
       </c>
       <c r="C2" t="n">
-        <v>11.80846138668064</v>
+        <v>7.734208414056373</v>
       </c>
       <c r="D2" t="n">
-        <v>21.71920446105219</v>
+        <v>26.57492860625691</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.11614932873739</v>
+        <v>17.02350519163969</v>
       </c>
       <c r="C3" t="n">
-        <v>37.47330987110075</v>
+        <v>26.52191423022758</v>
       </c>
       <c r="D3" t="n">
-        <v>35.55890184781947</v>
+        <v>40.35964812158637</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.10579207234717</v>
+        <v>24.69586350032851</v>
       </c>
       <c r="C4" t="n">
-        <v>76.1168630056637</v>
+        <v>42.71682435948296</v>
       </c>
       <c r="D4" t="n">
-        <v>29.02242563294421</v>
+        <v>35.65904011365264</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.72054606165493</v>
+        <v>22.2856728864026</v>
       </c>
       <c r="C5" t="n">
-        <v>95.03317777109126</v>
+        <v>45.70035563268903</v>
       </c>
       <c r="D5" t="n">
-        <v>27.243498792849</v>
+        <v>28.76520773443155</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.18366893615217</v>
+        <v>11.99499345048753</v>
       </c>
       <c r="C6" t="n">
-        <v>71.20517924131691</v>
+        <v>26.80760281216341</v>
       </c>
       <c r="D6" t="n">
-        <v>30.26924521733767</v>
+        <v>30.3497485290859</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.030475236560656</v>
+        <v>5.329908286355933</v>
       </c>
       <c r="C7" t="n">
-        <v>31.32069700858599</v>
+        <v>15.57051858935441</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>31.4404702285041</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
         <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5955,10 +5955,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.048858810213058</v>
+        <v>7.071111820629362</v>
       </c>
       <c r="C21" t="n">
-        <v>66.08305134574742</v>
+        <v>67.17556229597893</v>
       </c>
       <c r="D21" t="n">
-        <v>4.405536756383161</v>
+        <v>5.303333865472021</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.406083696659685</v>
+        <v>5.091343594223958</v>
       </c>
       <c r="C2" t="n">
-        <v>7.621307428067988</v>
+        <v>5.955281573961152</v>
       </c>
       <c r="D2" t="n">
-        <v>21.006455627769</v>
+        <v>21.72214970416493</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.77806826557799</v>
+        <v>22.01569226773472</v>
       </c>
       <c r="C3" t="n">
-        <v>42.95146206079795</v>
+        <v>29.01555339901448</v>
       </c>
       <c r="D3" t="n">
-        <v>45.20948178056562</v>
+        <v>53.60342465187585</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.94737083906494</v>
+        <v>30.45185029032756</v>
       </c>
       <c r="C4" t="n">
-        <v>87.20766682053993</v>
+        <v>58.19800390775092</v>
       </c>
       <c r="D4" t="n">
-        <v>40.91728081759857</v>
+        <v>49.2002861983289</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.15099352447154</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="C5" t="n">
-        <v>122.6202882604266</v>
+        <v>66.78338758138929</v>
       </c>
       <c r="D5" t="n">
-        <v>31.63681976935347</v>
+        <v>35.63744166415923</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.87173520810894</v>
+        <v>22.50067563363265</v>
       </c>
       <c r="C6" t="n">
-        <v>117.4543318406799</v>
+        <v>54.6214970211798</v>
       </c>
       <c r="D6" t="n">
-        <v>32.60384125803657</v>
+        <v>33.2881194078966</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.102764713776425</v>
+        <v>10.65981657271187</v>
       </c>
       <c r="C7" t="n">
-        <v>72.22325161062085</v>
+        <v>29.58398531977338</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>33.77604801690726</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>31.62700229231099</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.51874800293658</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>34.82848155585983</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>33.41280136633594</v>
       </c>
     </row>
     <row r="13">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6238,10 +6238,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6266,10 +6266,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.265169685733696</v>
+        <v>7.298444524603425</v>
       </c>
       <c r="C21" t="n">
-        <v>75.3761354894871</v>
+        <v>77.5459730739114</v>
       </c>
       <c r="D21" t="n">
-        <v>5.448877264300272</v>
+        <v>6.386138959027996</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.51171153809084</v>
+        <v>5.263149442467151</v>
       </c>
       <c r="C2" t="n">
-        <v>6.163412087261475</v>
+        <v>9.214683952060563</v>
       </c>
       <c r="D2" t="n">
-        <v>25.16023016443726</v>
+        <v>18.4224956701914</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.85522542358599</v>
+        <v>19.5613230071177</v>
       </c>
       <c r="C3" t="n">
-        <v>35.1023891653447</v>
+        <v>25.43217427851362</v>
       </c>
       <c r="D3" t="n">
-        <v>51.11960296013142</v>
+        <v>58.54161560423731</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.01417074068274</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="C4" t="n">
-        <v>98.77069128115886</v>
+        <v>66.91494177375834</v>
       </c>
       <c r="D4" t="n">
-        <v>53.24606848753</v>
+        <v>64.54107582488956</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.77149913128453</v>
+        <v>39.76078202199582</v>
       </c>
       <c r="C5" t="n">
-        <v>143.8751260573701</v>
+        <v>89.8790023237955</v>
       </c>
       <c r="D5" t="n">
-        <v>39.24536447726625</v>
+        <v>45.87216148093222</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.47929816831747</v>
+        <v>33.52962934314132</v>
       </c>
       <c r="C6" t="n">
-        <v>157.5449810913027</v>
+        <v>84.00520580928684</v>
       </c>
       <c r="D6" t="n">
-        <v>35.13969557810609</v>
+        <v>37.07177506006381</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.51063197939536</v>
+        <v>19.70269467652924</v>
       </c>
       <c r="C7" t="n">
-        <v>124.3844888849581</v>
+        <v>57.3713723407751</v>
       </c>
       <c r="D7" t="n">
-        <v>35.75230614555609</v>
+        <v>36.35117224514665</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.760715602071035</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="C8" t="n">
-        <v>65.42366701100744</v>
+        <v>31.12631096314512</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>31.8390597964283</v>
+        <v>25.18281036163492</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
         <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
         <v>35.53926689373453</v>
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
         <v>31.73990327829938</v>
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>18.18589447346791</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.466297652196379</v>
+        <v>7.513892317951878</v>
       </c>
       <c r="C21" t="n">
-        <v>83.99584858720925</v>
+        <v>87.34899819619058</v>
       </c>
       <c r="D21" t="n">
-        <v>6.533010445671831</v>
+        <v>7.513892317951878</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_8_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_8_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497645299279</v>
+        <v>10.84497638386175</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907236275674</v>
+        <v>37.78907212187122</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.393141050055229</v>
+        <v>1.311614932873739</v>
       </c>
       <c r="C2" t="n">
-        <v>5.662720758095602</v>
+        <v>1.672898088036565</v>
       </c>
       <c r="D2" t="n">
-        <v>23.52071149834508</v>
+        <v>18.29781371175205</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.89373456822987</v>
+        <v>9.881290643244148</v>
       </c>
       <c r="C3" t="n">
-        <v>31.38156536624929</v>
+        <v>23.38032157663779</v>
       </c>
       <c r="D3" t="n">
-        <v>59.51845456996288</v>
+        <v>96.98194696402118</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.54792269662352</v>
+        <v>16.56601076146068</v>
       </c>
       <c r="C4" t="n">
-        <v>65.08987279156354</v>
+        <v>90.56426222135977</v>
       </c>
       <c r="D4" t="n">
-        <v>78.56730527546374</v>
+        <v>110.8697499882965</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.30198704894308</v>
+        <v>17.64691498383642</v>
       </c>
       <c r="C5" t="n">
-        <v>108.11496593018</v>
+        <v>115.2817241711817</v>
       </c>
       <c r="D5" t="n">
-        <v>57.55495916146927</v>
+        <v>56.35231822376693</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.47807974090175</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="C6" t="n">
-        <v>113.9121861237574</v>
+        <v>70.03788122096746</v>
       </c>
       <c r="D6" t="n">
-        <v>43.14977509705582</v>
+        <v>30.5510068084565</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.06307819944583</v>
+        <v>6.048547605864599</v>
       </c>
       <c r="C7" t="n">
-        <v>91.0875337477233</v>
+        <v>39.70482240285375</v>
       </c>
       <c r="D7" t="n">
-        <v>38.74663664350886</v>
+        <v>28.98511922018283</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.43798264928109</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>54.24156065963627</v>
+        <v>28.95664853675967</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>31.04286240828414</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.543749359432489</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>32.72655972106742</v>
+        <v>31.06249736236907</v>
       </c>
       <c r="D9" t="n">
-        <v>34.50155957034565</v>
+        <v>35.05624702324509</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>3.274128593663113</v>
       </c>
       <c r="C10" t="n">
-        <v>29.32480392585223</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>38.00836236991527</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>37.31623023842126</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>28.20561154301086</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>37.5351599764683</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>26.01631416254048</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.25358797846125</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.715706076253899</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>96.44632595317374</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.680169335785637</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.504299524813371</v>
+        <v>1.730821202587127</v>
       </c>
       <c r="C2" t="n">
-        <v>8.565748719553421</v>
+        <v>4.887140071740622</v>
       </c>
       <c r="D2" t="n">
-        <v>26.61223501901829</v>
+        <v>15.42227468601314</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.17000658375072</v>
+        <v>7.009678608322226</v>
       </c>
       <c r="C3" t="n">
-        <v>26.31083847381452</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D3" t="n">
-        <v>63.41599295582272</v>
+        <v>89.31940613237481</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.87149852839745</v>
+        <v>18.11029990024091</v>
       </c>
       <c r="C4" t="n">
-        <v>71.1904530257532</v>
+        <v>72.6709285637574</v>
       </c>
       <c r="D4" t="n">
-        <v>87.84580282830034</v>
+        <v>133.2683238606875</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.98354093986863</v>
+        <v>21.45118733779281</v>
       </c>
       <c r="C5" t="n">
-        <v>114.029995848267</v>
+        <v>144.5132620651305</v>
       </c>
       <c r="D5" t="n">
-        <v>71.05399009486291</v>
+        <v>81.73049637854697</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.33973543006097</v>
+        <v>17.95223851985718</v>
       </c>
       <c r="C6" t="n">
-        <v>140.8405439035432</v>
+        <v>128.2417756149439</v>
       </c>
       <c r="D6" t="n">
-        <v>49.99255659565609</v>
+        <v>40.21140421824511</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.32176087174825</v>
+        <v>9.82140403328509</v>
       </c>
       <c r="C7" t="n">
-        <v>127.1392729430747</v>
+        <v>70.36676670189013</v>
       </c>
       <c r="D7" t="n">
-        <v>42.33983324105218</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.44904391593506</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>85.70166584222531</v>
+        <v>40.80634332701867</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.31562403914873</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>49.58905828921062</v>
+        <v>34.61249706092553</v>
       </c>
       <c r="D9" t="n">
-        <v>36.16562192904399</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>34.16482010778901</v>
+        <v>34.02246669067321</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>38.72012945549421</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>38.20471191076462</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>31.02617269731195</v>
+        <v>28.42257778564941</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>25.083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>50.2949348885641</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>45.7376620454504</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.902338218597078</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>105.6937736737359</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.877922773246347</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11.71617710248144</v>
+        <v>0.9149888603580273</v>
       </c>
       <c r="C2" t="n">
-        <v>7.903069019186824</v>
+        <v>2.043998720241859</v>
       </c>
       <c r="D2" t="n">
-        <v>20.53718022513903</v>
+        <v>10.55869655917445</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.30945581548277</v>
+        <v>7.191301933607886</v>
       </c>
       <c r="C3" t="n">
-        <v>29.48679229705295</v>
+        <v>17.26403337918016</v>
       </c>
       <c r="D3" t="n">
-        <v>68.16765184437729</v>
+        <v>85.56422116363076</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.89702396870788</v>
+        <v>20.02470792352219</v>
       </c>
       <c r="C4" t="n">
-        <v>68.44646819238336</v>
+        <v>63.89017709697393</v>
       </c>
       <c r="D4" t="n">
-        <v>96.99667317958487</v>
+        <v>146.0565694562065</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.21072557017713</v>
+        <v>21.89297380470387</v>
       </c>
       <c r="C5" t="n">
-        <v>120.4358996184775</v>
+        <v>161.0311671890831</v>
       </c>
       <c r="D5" t="n">
-        <v>82.29500130848889</v>
+        <v>92.92242020696061</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.7460401108989</v>
+        <v>14.04782790006761</v>
       </c>
       <c r="C6" t="n">
-        <v>157.665736058925</v>
+        <v>163.6632327841688</v>
       </c>
       <c r="D6" t="n">
-        <v>58.88817254383644</v>
+        <v>40.57366912111219</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>51.3228247349105</v>
+        <v>4.251949307092936</v>
       </c>
       <c r="C7" t="n">
-        <v>161.7537334994087</v>
+        <v>67.97130230352791</v>
       </c>
       <c r="D7" t="n">
-        <v>45.87314322863646</v>
+        <v>33.11729530735765</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>32.54493639578176</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>121.5010958775852</v>
+        <v>39.8884092235479</v>
       </c>
       <c r="D8" t="n">
-        <v>40.80634332701867</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.52968609640354</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>74.77186865084555</v>
+        <v>25.95937279569415</v>
       </c>
       <c r="D9" t="n">
-        <v>37.27499683484289</v>
+        <v>40.60312155223957</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.398851609831464</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>44.69897297435728</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>36.15776794741003</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>35.7169632282032</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>37.31623023842126</v>
+        <v>30.38607319414302</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.95941385342317</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>33.82120841130262</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
         <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>20.30548776693678</v>
+        <v>43.44429940832985</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>19.26188995732242</v>
+        <v>39.59388491227386</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>19.25796296650543</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.072979141733866</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>114.0308303769908</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.10034631988406</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.41830663746715</v>
+        <v>1.080904222375738</v>
       </c>
       <c r="C2" t="n">
-        <v>5.310273332270997</v>
+        <v>4.113522880794135</v>
       </c>
       <c r="D2" t="n">
-        <v>16.78886749032471</v>
+        <v>12.3572583533546</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.47559216167874</v>
+        <v>5.109996800604648</v>
       </c>
       <c r="C3" t="n">
-        <v>43.72213400863171</v>
+        <v>12.03622685406589</v>
       </c>
       <c r="D3" t="n">
-        <v>74.74536146283091</v>
+        <v>75.3785887320701</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.56372847088269</v>
+        <v>17.24243492968673</v>
       </c>
       <c r="C4" t="n">
-        <v>98.88555576255573</v>
+        <v>53.13120400613313</v>
       </c>
       <c r="D4" t="n">
-        <v>93.41034881597128</v>
+        <v>154.8117954826795</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.77841242294326</v>
+        <v>26.06540154775282</v>
       </c>
       <c r="C5" t="n">
-        <v>94.19869222248147</v>
+        <v>140.1690284738384</v>
       </c>
       <c r="D5" t="n">
-        <v>58.09492039880502</v>
+        <v>120.7549676223577</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.83905979642831</v>
+        <v>20.89060939866788</v>
       </c>
       <c r="C6" t="n">
-        <v>106.5058814429195</v>
+        <v>212.4079880477272</v>
       </c>
       <c r="D6" t="n">
-        <v>30.18874190558942</v>
+        <v>57.60011955586462</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.55917958525995</v>
+        <v>8.92310488389926</v>
       </c>
       <c r="C7" t="n">
-        <v>85.39830580161305</v>
+        <v>146.6623077897268</v>
       </c>
       <c r="D7" t="n">
-        <v>28.68568617038755</v>
+        <v>36.47094546506476</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.43245201595411</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>55.07604620824605</v>
+        <v>62.66986470059513</v>
       </c>
       <c r="D8" t="n">
-        <v>27.45457454926205</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>36.72030938194344</v>
       </c>
       <c r="D9" t="n">
-        <v>27.5124976638126</v>
+        <v>41.71249645803847</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>27.90126975469435</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>29.18245050873644</v>
+        <v>31.60245859970483</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.25371718051895</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>27.55471281509523</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>20.58823110575986</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>23.29196428325557</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>36.78510473042374</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>47.22206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.628981483252716</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.027930904075415</v>
+        <v>0.5792311455056182</v>
       </c>
       <c r="C2" t="n">
-        <v>2.980586030093316</v>
+        <v>2.41313585703866</v>
       </c>
       <c r="D2" t="n">
-        <v>11.31955102996572</v>
+        <v>10.42419712369263</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>32.85418692261951</v>
+        <v>4.5553093477052</v>
       </c>
       <c r="C3" t="n">
-        <v>32.24059460746525</v>
+        <v>14.39733008277947</v>
       </c>
       <c r="D3" t="n">
-        <v>72.35971454151115</v>
+        <v>69.18376071827272</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.18605870438394</v>
+        <v>14.67712817848981</v>
       </c>
       <c r="C4" t="n">
-        <v>107.71735810996</v>
+        <v>43.48258756879548</v>
       </c>
       <c r="D4" t="n">
-        <v>107.8577480316673</v>
+        <v>159.3936120183994</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.50905369908114</v>
+        <v>27.61165418194155</v>
       </c>
       <c r="C5" t="n">
-        <v>137.2728727463103</v>
+        <v>126.9399781591126</v>
       </c>
       <c r="D5" t="n">
-        <v>72.60024272905164</v>
+        <v>140.3162906294754</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.11831811279092</v>
+        <v>25.23778823307276</v>
       </c>
       <c r="C6" t="n">
-        <v>128.966305420678</v>
+        <v>227.3413523770254</v>
       </c>
       <c r="D6" t="n">
-        <v>36.95102009244145</v>
+        <v>73.37876865851936</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.4213339960379</v>
+        <v>10.00106386316226</v>
       </c>
       <c r="C7" t="n">
-        <v>113.6048990923282</v>
+        <v>206.4291445288641</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20092378866788</v>
+        <v>40.78278138211675</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>73.76852249710534</v>
+        <v>97.88515485192822</v>
       </c>
       <c r="D8" t="n">
-        <v>28.37250865273282</v>
+        <v>40.22220344299182</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>40.71405904281946</v>
+        <v>47.25937098703294</v>
       </c>
       <c r="D9" t="n">
-        <v>28.84374755077128</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>32.59893251951534</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>32.69612554223576</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>23.21538796232432</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>31.17539834835746</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>8.025787482217675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.495242811296897</v>
+        <v>0.8816094384136358</v>
       </c>
       <c r="C2" t="n">
-        <v>6.975317438673588</v>
+        <v>4.977460860531329</v>
       </c>
       <c r="D2" t="n">
-        <v>10.39376294486098</v>
+        <v>13.28795517698058</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.56118413839745</v>
+        <v>3.259402378099411</v>
       </c>
       <c r="C3" t="n">
-        <v>20.86213871524472</v>
+        <v>11.83005983617407</v>
       </c>
       <c r="D3" t="n">
-        <v>65.10950774564847</v>
+        <v>62.21335201812037</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.80838893788518</v>
+        <v>11.88209246449915</v>
       </c>
       <c r="C4" t="n">
-        <v>94.3420273873015</v>
+        <v>39.66653424238812</v>
       </c>
       <c r="D4" t="n">
-        <v>118.4508057604904</v>
+        <v>157.8876110400848</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.44295780772712</v>
+        <v>25.45180923259857</v>
       </c>
       <c r="C5" t="n">
-        <v>167.9524885040231</v>
+        <v>104.3352372688298</v>
       </c>
       <c r="D5" t="n">
-        <v>92.38245896962486</v>
+        <v>161.5711284264189</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.80009298789471</v>
+        <v>30.67176177607885</v>
       </c>
       <c r="C6" t="n">
-        <v>173.2431268822092</v>
+        <v>218.8885046434604</v>
       </c>
       <c r="D6" t="n">
-        <v>49.06676851055134</v>
+        <v>94.95365620704727</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.02126395879071</v>
+        <v>17.96598298771663</v>
       </c>
       <c r="C7" t="n">
-        <v>149.1775454080071</v>
+        <v>261.8841453509494</v>
       </c>
       <c r="D7" t="n">
-        <v>34.37491411649782</v>
+        <v>49.70588626601601</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.52004854581032</v>
+        <v>6.67588438887831</v>
       </c>
       <c r="C8" t="n">
-        <v>109.2341583130213</v>
+        <v>174.9916195434727</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>41.8911745402114</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.434374453633594</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>63.01249464937726</v>
+        <v>78.5437433305618</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>42.48905889209769</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>39.28954312395736</v>
+        <v>42.27896488338889</v>
       </c>
       <c r="D10" t="n">
-        <v>30.89069151412589</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>26.25291535926396</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
+        <v>20.28094407433061</v>
+      </c>
+      <c r="D14" t="n">
         <v>16.90078672860884</v>
-      </c>
-      <c r="D14" t="n">
-        <v>20.28094407433061</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.803290606252143</v>
+        <v>0.5919938656608267</v>
       </c>
       <c r="C2" t="n">
-        <v>3.189698291097887</v>
+        <v>2.588868696098839</v>
       </c>
       <c r="D2" t="n">
-        <v>7.176575718044184</v>
+        <v>9.567131377885167</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.02751429791469</v>
+        <v>4.584761778832604</v>
       </c>
       <c r="C3" t="n">
-        <v>25.01493150420873</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D3" t="n">
-        <v>62.07099860100459</v>
+        <v>67.95166734944299</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>56.43674852633215</v>
+        <v>18.12306262039612</v>
       </c>
       <c r="C4" t="n">
-        <v>87.96066730969723</v>
+        <v>57.15146085502382</v>
       </c>
       <c r="D4" t="n">
-        <v>125.4064882450791</v>
+        <v>162.5332411765807</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.38190952361457</v>
+        <v>19.1440802328128</v>
       </c>
       <c r="C5" t="n">
-        <v>194.1406085148068</v>
+        <v>171.2167996206437</v>
       </c>
       <c r="D5" t="n">
-        <v>100.3591590666302</v>
+        <v>146.6485633218673</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.8768081775462</v>
+        <v>11.14970867713103</v>
       </c>
       <c r="C6" t="n">
-        <v>211.9249681772378</v>
+        <v>226.0935510449277</v>
       </c>
       <c r="D6" t="n">
-        <v>48.70450360768427</v>
+        <v>76.1963845697077</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>4.371722527011046</v>
       </c>
       <c r="C7" t="n">
-        <v>153.0701750553457</v>
+        <v>123.0669834658589</v>
       </c>
       <c r="D7" t="n">
-        <v>34.73423377625215</v>
+        <v>36.71049190490098</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>2.253110981246429</v>
       </c>
       <c r="C8" t="n">
-        <v>80.69475255056658</v>
+        <v>57.82984851865836</v>
       </c>
       <c r="D8" t="n">
-        <v>31.96079651175491</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>29.95312245657017</v>
+        <v>32.28280975874785</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>26.5140602485936</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>26.1930287493049</v>
+        <v>24.20008090968388</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>25.90832191507333</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.96816746730337</v>
+        <v>21.14586380177204</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
+        <v>16.65044106402591</v>
+      </c>
+      <c r="D13" t="n">
         <v>13.78864650614645</v>
-      </c>
-      <c r="D13" t="n">
-        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>35.1171153809084</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.919578803709772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>6.138868394655306</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.275511251994859</v>
+        <v>0.321031499288707</v>
       </c>
       <c r="C2" t="n">
-        <v>7.118652603493622</v>
+        <v>2.057743188101315</v>
       </c>
       <c r="D2" t="n">
-        <v>12.40143700004571</v>
+        <v>6.842781498600268</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.20436775339936</v>
+        <v>3.288854809226815</v>
       </c>
       <c r="C3" t="n">
-        <v>18.51085296357361</v>
+        <v>12.9443434804942</v>
       </c>
       <c r="D3" t="n">
-        <v>54.33482669153972</v>
+        <v>60.18113427032947</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>54.22879793948106</v>
+        <v>12.64785567381166</v>
       </c>
       <c r="C4" t="n">
-        <v>75.12137083355744</v>
+        <v>47.17101369365075</v>
       </c>
       <c r="D4" t="n">
-        <v>127.4612861900676</v>
+        <v>153.5482861873139</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.77080478768333</v>
+        <v>18.30959468420302</v>
       </c>
       <c r="C5" t="n">
-        <v>180.4452280405638</v>
+        <v>125.0992012136498</v>
       </c>
       <c r="D5" t="n">
-        <v>118.9141906768949</v>
+        <v>153.6189720220197</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.87180162803373</v>
+        <v>11.14970867713103</v>
       </c>
       <c r="C6" t="n">
-        <v>257.9728624972302</v>
+        <v>207.8595509339517</v>
       </c>
       <c r="D6" t="n">
-        <v>65.20768251607315</v>
+        <v>83.15992103593032</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.43940636534185</v>
+        <v>3.772856427420492</v>
       </c>
       <c r="C7" t="n">
-        <v>222.7781890476862</v>
+        <v>155.2260930138717</v>
       </c>
       <c r="D7" t="n">
-        <v>39.16584291322225</v>
+        <v>36.71049190490098</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>131.5983710157637</v>
+        <v>66.25815255961723</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>26.78698611037422</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>56.57812019574367</v>
+        <v>30.17499743772996</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>21.29999819133879</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>17.93653055658923</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>19.78712497909446</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.52209415667683</v>
+        <v>13.50492141961912</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.44249047717483</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>24.38563122578652</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.145519644406781</v>
+        <v>0.7520187414530567</v>
       </c>
       <c r="C2" t="n">
-        <v>3.726714285320892</v>
+        <v>5.994551482131024</v>
       </c>
       <c r="D2" t="n">
-        <v>8.823948365770333</v>
+        <v>15.68047433223006</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.02979658849267</v>
+        <v>2.086213871524472</v>
       </c>
       <c r="C3" t="n">
-        <v>23.2232419439583</v>
+        <v>9.950012982541423</v>
       </c>
       <c r="D3" t="n">
-        <v>52.29770020522759</v>
+        <v>51.68901662859457</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.44277788127786</v>
+        <v>9.418887474543899</v>
       </c>
       <c r="C4" t="n">
-        <v>63.8518889365083</v>
+        <v>38.97734735400687</v>
       </c>
       <c r="D4" t="n">
-        <v>126.6572348202895</v>
+        <v>149.4386902973367</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>71.8884756434727</v>
+        <v>18.94773069196344</v>
       </c>
       <c r="C5" t="n">
-        <v>170.1368771459722</v>
+        <v>103.9916255723434</v>
       </c>
       <c r="D5" t="n">
-        <v>132.1186972990145</v>
+        <v>174.7756350485384</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.25672884355649</v>
+        <v>18.07299348747954</v>
       </c>
       <c r="C6" t="n">
-        <v>280.7955513778558</v>
+        <v>206.1689813872387</v>
       </c>
       <c r="D6" t="n">
-        <v>76.88066271956774</v>
+        <v>111.1750735243173</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.12190094624263</v>
+        <v>8.324238784308704</v>
       </c>
       <c r="C7" t="n">
-        <v>278.9518291892802</v>
+        <v>233.6176654502752</v>
       </c>
       <c r="D7" t="n">
-        <v>43.77711188006952</v>
+        <v>50.783845245279</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C8" t="n">
-        <v>174.5743767691678</v>
+        <v>136.7721814171444</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>30.29182541453534</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>68.33749419721195</v>
+        <v>56.79999517690344</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>23.2968730217768</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>20.4988920646734</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>17.05884810899257</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>13.23494080095125</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96750451476862</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>7.525096153051802</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.532148313430777</v>
+        <v>1.034762080276138</v>
       </c>
       <c r="C2" t="n">
-        <v>10.05604173460008</v>
+        <v>4.378594760940774</v>
       </c>
       <c r="D2" t="n">
-        <v>9.690831588620265</v>
+        <v>15.74625142841459</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.45623494503428</v>
+        <v>2.32674205906494</v>
       </c>
       <c r="C3" t="n">
-        <v>19.1146278016854</v>
+        <v>17.33766445699867</v>
       </c>
       <c r="D3" t="n">
-        <v>47.96819282949916</v>
+        <v>51.97863220134738</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.57643443777567</v>
+        <v>6.649377200863647</v>
       </c>
       <c r="C4" t="n">
-        <v>61.01856506205201</v>
+        <v>31.37076614150258</v>
       </c>
       <c r="D4" t="n">
-        <v>124.1429789497134</v>
+        <v>140.8493796328814</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>72.69841749947632</v>
+        <v>16.95969159086365</v>
       </c>
       <c r="C5" t="n">
-        <v>147.041262403566</v>
+        <v>87.3264582927538</v>
       </c>
       <c r="D5" t="n">
-        <v>141.7889121858456</v>
+        <v>188.9128019896925</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>74.38506005537235</v>
+        <v>21.77614582789851</v>
       </c>
       <c r="C6" t="n">
-        <v>277.6559222196745</v>
+        <v>186.8884382235356</v>
       </c>
       <c r="D6" t="n">
-        <v>94.63164296005432</v>
+        <v>138.2644379275996</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.72856427420492</v>
+        <v>14.67221943996858</v>
       </c>
       <c r="C7" t="n">
-        <v>331.8915923930852</v>
+        <v>265.5971151684108</v>
       </c>
       <c r="D7" t="n">
-        <v>52.28101049425539</v>
+        <v>67.73175586369169</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.2641722479004</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>253.8505038870977</v>
+        <v>223.6421270274234</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.773437264497239</v>
+        <v>1.442187377538564</v>
       </c>
       <c r="C9" t="n">
-        <v>123.473427015417</v>
+        <v>111.8249905045287</v>
       </c>
       <c r="D9" t="n">
-        <v>34.50155957034565</v>
+        <v>25.5156228333746</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>49.11192890494669</v>
+        <v>45.98015372839937</v>
       </c>
       <c r="D10" t="n">
-        <v>26.90479583488384</v>
+        <v>21.49536598448391</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>18.8358114536793</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.29148125717007</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.881249585515142</v>
+        <v>5.102142818970673</v>
       </c>
       <c r="C2" t="n">
-        <v>2.916772429317273</v>
+        <v>9.063494805606554</v>
       </c>
       <c r="D2" t="n">
-        <v>6.90364985626357</v>
+        <v>8.759153017290043</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.914228096832033</v>
+        <v>0.9709484795000954</v>
       </c>
       <c r="C2" t="n">
-        <v>5.711808143307943</v>
+        <v>12.30817096814226</v>
       </c>
       <c r="D2" t="n">
-        <v>7.132397071353077</v>
+        <v>20.68247888536755</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.13073667558085</v>
+        <v>2.861794557879453</v>
       </c>
       <c r="C3" t="n">
-        <v>27.9945357865978</v>
+        <v>17.07750131537327</v>
       </c>
       <c r="D3" t="n">
-        <v>52.3566050674824</v>
+        <v>52.12098561846316</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>56.73029108990194</v>
+        <v>5.500732386894879</v>
       </c>
       <c r="C4" t="n">
-        <v>87.30976858178158</v>
+        <v>37.29266829351933</v>
       </c>
       <c r="D4" t="n">
-        <v>127.8186423544135</v>
+        <v>135.6294270894011</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.9086660724386</v>
+        <v>14.06353586333556</v>
       </c>
       <c r="C5" t="n">
-        <v>227.0537002996811</v>
+        <v>73.06657288856887</v>
       </c>
       <c r="D5" t="n">
-        <v>131.7014545247096</v>
+        <v>193.9197152813513</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.42646371873739</v>
+        <v>22.42017232188442</v>
       </c>
       <c r="C6" t="n">
-        <v>275.7238427377167</v>
+        <v>163.9449943752876</v>
       </c>
       <c r="D6" t="n">
-        <v>76.31713953733006</v>
+        <v>162.7374446990641</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.767186925373263</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="C7" t="n">
-        <v>178.5219842879443</v>
+        <v>270.9270234547668</v>
       </c>
       <c r="D7" t="n">
-        <v>33.65627479698915</v>
+        <v>86.6559246107532</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.919316761802514</v>
+        <v>9.846929473595507</v>
       </c>
       <c r="C8" t="n">
-        <v>90.95892479846698</v>
+        <v>285.2271605148258</v>
       </c>
       <c r="D8" t="n">
-        <v>25.36836067773758</v>
+        <v>44.39463118604076</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>37.49687181600267</v>
+        <v>185.1546717778357</v>
       </c>
       <c r="D9" t="n">
-        <v>20.52343575727956</v>
+        <v>28.28906009787183</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
+        <v>84.13086951543042</v>
+      </c>
+      <c r="D10" t="n">
         <v>22.49183990429443</v>
-      </c>
-      <c r="D10" t="n">
-        <v>19.07535789351553</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.8811517745239</v>
+        <v>36.07235589714055</v>
       </c>
       <c r="D11" t="n">
-        <v>16.8811517745239</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>15.4046032273367</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>16.1301147807751</v>
+      </c>
+      <c r="D13" t="n">
         <v>10.14636252339079</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.838453597155781</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.376451339083034</v>
+        <v>4.956844158742146</v>
       </c>
       <c r="C2" t="n">
-        <v>5.597925409615312</v>
+        <v>7.312056901230244</v>
       </c>
       <c r="D2" t="n">
-        <v>8.943721585688444</v>
+        <v>30.66783478526186</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.37216449536755</v>
+        <v>8.423395302437633</v>
       </c>
       <c r="C3" t="n">
-        <v>7.466191290796992</v>
+        <v>17.89235190989812</v>
       </c>
       <c r="D3" t="n">
-        <v>9.208793465835081</v>
+        <v>9.017352663506953</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39948063089694</v>
+        <v>11.6780929677617</v>
       </c>
       <c r="C21" t="n">
-        <v>70.15022212646045</v>
+        <v>59.94754390117674</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576409485987875</v>
+        <v>0.7785395311841136</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.819800390775092</v>
+        <v>2.850995333132738</v>
       </c>
       <c r="C2" t="n">
-        <v>6.699446333780234</v>
+        <v>6.989061906533043</v>
       </c>
       <c r="D2" t="n">
-        <v>20.52539925268806</v>
+        <v>33.08980637163874</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.59291886010284</v>
+        <v>14.00463100108075</v>
       </c>
       <c r="C3" t="n">
-        <v>16.6062624173348</v>
+        <v>25.01984024272996</v>
       </c>
       <c r="D3" t="n">
-        <v>14.49550485320416</v>
+        <v>33.73775985644163</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.13734686760332</v>
+        <v>10.43990508696058</v>
       </c>
       <c r="C4" t="n">
-        <v>12.1118214272929</v>
+        <v>29.64779892054943</v>
       </c>
       <c r="D4" t="n">
-        <v>19.89708072197011</v>
+        <v>18.93987671032947</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.105088062083415</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.36836067773758</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.84843530511426</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.87534340375643</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44683123740853</v>
+        <v>13.62705429548758</v>
       </c>
       <c r="C21" t="n">
-        <v>86.17705848238441</v>
+        <v>73.74641148146216</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251964471033374</v>
+        <v>1.603182858292656</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.16791991515521</v>
+        <v>1.742602175038088</v>
       </c>
       <c r="C2" t="n">
-        <v>5.65093978564464</v>
+        <v>7.156940763959247</v>
       </c>
       <c r="D2" t="n">
-        <v>19.22458354456104</v>
+        <v>31.26866438026091</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.1293540172491</v>
+        <v>11.77606371244049</v>
       </c>
       <c r="C3" t="n">
-        <v>22.61455836732528</v>
+        <v>26.45810062945154</v>
       </c>
       <c r="D3" t="n">
-        <v>27.55274931968674</v>
+        <v>53.37762267989908</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.86177886234622</v>
+        <v>20.26719960647115</v>
       </c>
       <c r="C4" t="n">
-        <v>29.32873091666921</v>
+        <v>50.0936766091935</v>
       </c>
       <c r="D4" t="n">
-        <v>22.51343835378785</v>
+        <v>32.22586839190155</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.06920536538279</v>
+        <v>9.719302272043425</v>
       </c>
       <c r="C5" t="n">
-        <v>15.24163310843173</v>
+        <v>34.87658719336795</v>
       </c>
       <c r="D5" t="n">
-        <v>29.96784867213389</v>
+        <v>26.72808124811942</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.54593383901924</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.886960145291375</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.219371706403542</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.95717262057418</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.95035713990669</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74652418251343</v>
+        <v>14.83337105026868</v>
       </c>
       <c r="C21" t="n">
-        <v>102.153797513332</v>
+        <v>87.35207396269337</v>
       </c>
       <c r="D21" t="n">
-        <v>5.023957254754031</v>
+        <v>2.472228508378114</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.658793767278616</v>
+        <v>1.97920337176157</v>
       </c>
       <c r="C2" t="n">
-        <v>8.353691215436109</v>
+        <v>6.10352547730242</v>
       </c>
       <c r="D2" t="n">
-        <v>19.57997621349838</v>
+        <v>40.49611105247669</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.55994034878595</v>
+        <v>8.531387549904784</v>
       </c>
       <c r="C3" t="n">
-        <v>22.21695054710532</v>
+        <v>27.3024036551038</v>
       </c>
       <c r="D3" t="n">
-        <v>36.03504948437918</v>
+        <v>66.00780689503431</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.34524070119216</v>
+        <v>21.92635322664826</v>
       </c>
       <c r="C4" t="n">
-        <v>44.83543590524759</v>
+        <v>59.64019128528948</v>
       </c>
       <c r="D4" t="n">
-        <v>30.56671477172444</v>
+        <v>51.70177934874977</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.44551783574558</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="C5" t="n">
-        <v>36.49647090537518</v>
+        <v>67.76513528563609</v>
       </c>
       <c r="D5" t="n">
-        <v>31.46501392111028</v>
+        <v>32.07860623626453</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.465430527271</v>
+        <v>9.096874227550947</v>
       </c>
       <c r="C6" t="n">
-        <v>18.67676832559133</v>
+        <v>35.01894061048373</v>
       </c>
       <c r="D6" t="n">
-        <v>37.91705983342032</v>
+        <v>33.65038431076368</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>25.70215489718149</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.46563581591602</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>27.62343515439249</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.27499683484289</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.574764375340887</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>45.4902616239802</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.58536797810513</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.63820242768521</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.08183501354747</v>
+        <v>16.06963148546344</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9624474693335</v>
+        <v>100.6466393036921</v>
       </c>
       <c r="D21" t="n">
-        <v>6.888318100399035</v>
+        <v>3.383080312729145</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.10392638792992</v>
+        <v>1.687624303600267</v>
       </c>
       <c r="C2" t="n">
-        <v>7.734208414056373</v>
+        <v>4.82627171407732</v>
       </c>
       <c r="D2" t="n">
-        <v>26.57492860625691</v>
+        <v>35.3478260914064</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.02350519163969</v>
+        <v>7.564366061221674</v>
       </c>
       <c r="C3" t="n">
-        <v>26.52191423022758</v>
+        <v>25.22109852210056</v>
       </c>
       <c r="D3" t="n">
-        <v>40.35964812158637</v>
+        <v>82.10356050616076</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.69586350032851</v>
+        <v>19.1440802328128</v>
       </c>
       <c r="C4" t="n">
-        <v>42.71682435948296</v>
+        <v>64.38792318302706</v>
       </c>
       <c r="D4" t="n">
-        <v>35.65904011365264</v>
+        <v>71.99450439553134</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.2856728864026</v>
+        <v>26.55627539987623</v>
       </c>
       <c r="C5" t="n">
-        <v>45.70035563268903</v>
+        <v>89.55993431991529</v>
       </c>
       <c r="D5" t="n">
-        <v>28.76520773443155</v>
+        <v>42.73056882734243</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.99499345048753</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="C6" t="n">
-        <v>26.80760281216341</v>
+        <v>72.6139871969111</v>
       </c>
       <c r="D6" t="n">
-        <v>30.3497485290859</v>
+        <v>35.94472869558847</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.329908286355933</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>15.57051858935441</v>
+        <v>34.49468733641593</v>
       </c>
       <c r="D7" t="n">
-        <v>31.4404702285041</v>
+        <v>37.12969817461437</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.098436812331936</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>30.50780990946962</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>38.38437174064178</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>6.930157044278233</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>45.84565429291754</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>5.858088551240717</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.071111820629362</v>
+        <v>17.32782748579053</v>
       </c>
       <c r="C21" t="n">
-        <v>67.17556229597893</v>
+        <v>114.3636614062175</v>
       </c>
       <c r="D21" t="n">
-        <v>5.303333865472021</v>
+        <v>4.331956871447632</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.091343594223958</v>
+        <v>3.013965452037707</v>
       </c>
       <c r="C2" t="n">
-        <v>5.955281573961152</v>
+        <v>5.493860152965151</v>
       </c>
       <c r="D2" t="n">
-        <v>21.72214970416493</v>
+        <v>33.70045344368026</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.01569226773472</v>
+        <v>6.572800879932396</v>
       </c>
       <c r="C3" t="n">
-        <v>29.01555339901448</v>
+        <v>21.65735435568464</v>
       </c>
       <c r="D3" t="n">
-        <v>53.60342465187585</v>
+        <v>90.0802606031661</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.45185029032756</v>
+        <v>16.65534980254714</v>
       </c>
       <c r="C4" t="n">
-        <v>58.19800390775092</v>
+        <v>63.63492269386975</v>
       </c>
       <c r="D4" t="n">
-        <v>49.2002861983289</v>
+        <v>94.25268834621504</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.31775176547326</v>
+        <v>27.88163480060942</v>
       </c>
       <c r="C5" t="n">
-        <v>66.78338758138929</v>
+        <v>104.1388877279804</v>
       </c>
       <c r="D5" t="n">
-        <v>35.63744166415923</v>
+        <v>57.0395416167397</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.50067563363265</v>
+        <v>26.3648345975481</v>
       </c>
       <c r="C6" t="n">
-        <v>54.6214970211798</v>
+        <v>105.3788350784441</v>
       </c>
       <c r="D6" t="n">
-        <v>33.2881194078966</v>
+        <v>40.33215918586747</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.65981657271187</v>
+        <v>14.79199265988669</v>
       </c>
       <c r="C7" t="n">
-        <v>29.58398531977338</v>
+        <v>68.33062196328224</v>
       </c>
       <c r="D7" t="n">
-        <v>33.77604801690726</v>
+        <v>39.28561613314036</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>8.595201150680824</v>
       </c>
       <c r="C8" t="n">
-        <v>20.36144738607885</v>
+        <v>35.21529015133309</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.51874800293658</v>
+        <v>31.39530983410874</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>39.49374664644068</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>34.02246669067321</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.298444524603425</v>
+        <v>17.71766252421762</v>
       </c>
       <c r="C21" t="n">
-        <v>77.5459730739114</v>
+        <v>126.681287048156</v>
       </c>
       <c r="D21" t="n">
-        <v>6.386138959027996</v>
+        <v>5.315298757265286</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.263149442467151</v>
+        <v>2.635010838198439</v>
       </c>
       <c r="C2" t="n">
-        <v>9.214683952060563</v>
+        <v>3.427281235525615</v>
       </c>
       <c r="D2" t="n">
-        <v>18.4224956701914</v>
+        <v>26.76636940858504</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.5613230071177</v>
+        <v>9.935286766977722</v>
       </c>
       <c r="C3" t="n">
-        <v>25.43217427851362</v>
+        <v>34.08137155292803</v>
       </c>
       <c r="D3" t="n">
-        <v>58.54161560423731</v>
+        <v>97.53172567839937</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.61173629739955</v>
+        <v>13.38809344281375</v>
       </c>
       <c r="C4" t="n">
-        <v>66.91494177375834</v>
+        <v>91.0747710275681</v>
       </c>
       <c r="D4" t="n">
-        <v>64.54107582488956</v>
+        <v>84.17013942360029</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.76078202199582</v>
+        <v>14.84893402673301</v>
       </c>
       <c r="C5" t="n">
-        <v>89.8790023237955</v>
+        <v>62.95457153482673</v>
       </c>
       <c r="D5" t="n">
-        <v>45.87216148093222</v>
+        <v>40.5216364927871</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.52962934314132</v>
+        <v>9.177377539299185</v>
       </c>
       <c r="C6" t="n">
-        <v>84.00520580928684</v>
+        <v>45.00135126726531</v>
       </c>
       <c r="D6" t="n">
-        <v>37.07177506006381</v>
+        <v>25.84156307118455</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.70269467652924</v>
+        <v>5.689227946110266</v>
       </c>
       <c r="C7" t="n">
-        <v>57.3713723407751</v>
+        <v>24.73316991308989</v>
       </c>
       <c r="D7" t="n">
-        <v>36.35117224514665</v>
+        <v>26.82920126165683</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.012443924985718</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>31.12631096314512</v>
+        <v>23.11524969649115</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>25.18281036163492</v>
+        <v>25.95937279569415</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>33.61405964570653</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>18.18589447346791</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>30.17205219461722</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>96.16709636949629</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.513892317951878</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>87.34899819619058</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.513892317951878</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
